--- a/Presupuesto_Tecnologia_Bolivar_2026.xlsx
+++ b/Presupuesto_Tecnologia_Bolivar_2026.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00;-#,##0.00;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,12 +46,13 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -66,19 +67,8 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00AAAAAA"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00E8682A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00AAAAAA"/>
       <sz val="9"/>
     </font>
     <font>
@@ -143,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -163,10 +153,10 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -178,34 +168,22 @@
     <xf numFmtId="164" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -611,8 +589,8 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
     <col width="12" customWidth="1" min="32" max="32"/>
-    <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -622,15 +600,15 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Hoja Tecnologia · Reporte Ene–May 2026 · Intelisis ERP + Presupuesto</t>
+          <t>Hoja Tecnologia · Ene–May 2026 · Intelisis ERP + Presupuesto</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="22" customHeight="1">
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Concepto</t>
@@ -802,7 +780,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>UDESA-SUSCRIPCIONES DE SOFTWARE</t>
@@ -850,17 +828,17 @@
       <c r="K5" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="L5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="N5" s="11" t="n"/>
+      <c r="N5" s="10" t="n"/>
       <c r="O5" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="P5" s="11" t="n"/>
+      <c r="P5" s="10" t="n"/>
       <c r="Q5" s="9" t="n">
         <v>3000</v>
       </c>
@@ -870,147 +848,147 @@
       <c r="S5" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="T5" s="11" t="n">
+      <c r="T5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="U5" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="V5" s="11" t="n">
+      <c r="V5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="X5" s="11" t="n">
+      <c r="X5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="Z5" s="11" t="n">
+      <c r="Z5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AA5" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="AB5" s="11" t="n">
+      <c r="AB5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AC5" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="AD5" s="11" t="n">
+      <c r="AD5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AE5" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="AF5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="12" t="n">
+      <c r="AF5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="11" t="n">
         <v>36000</v>
       </c>
-      <c r="AH5" s="12" t="n">
+      <c r="AH5" s="11" t="n">
         <v>17691.94</v>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>UDESA-SUSCRIPCIONES DE SOFTWARE</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Suscripciones y publicaciones</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>412010905</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>Kaspersky IB</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>Grupo Octo</t>
         </is>
       </c>
-      <c r="I6" s="15" t="n"/>
+      <c r="I6" s="14" t="n"/>
       <c r="J6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="15" t="n"/>
+      <c r="K6" s="14" t="n"/>
       <c r="L6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="15" t="n"/>
+      <c r="M6" s="14" t="n"/>
       <c r="N6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="15" t="n"/>
+      <c r="O6" s="14" t="n"/>
       <c r="P6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="15" t="n"/>
+      <c r="Q6" s="14" t="n"/>
       <c r="R6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="15" t="n"/>
+      <c r="S6" s="14" t="n"/>
       <c r="T6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U6" s="15" t="n"/>
+      <c r="U6" s="14" t="n"/>
       <c r="V6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="15" t="n"/>
+      <c r="W6" s="14" t="n"/>
       <c r="X6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y6" s="15" t="n"/>
+      <c r="Y6" s="14" t="n"/>
       <c r="Z6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA6" s="15" t="n"/>
+      <c r="AA6" s="14" t="n"/>
       <c r="AB6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC6" s="16" t="n">
+      <c r="AC6" s="14" t="n">
         <v>500</v>
       </c>
       <c r="AD6" s="15" t="n"/>
-      <c r="AE6" s="15" t="n"/>
+      <c r="AE6" s="14" t="n"/>
       <c r="AF6" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG6" s="17" t="n">
+      <c r="AG6" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="AH6" s="18" t="n">
+      <c r="AH6" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>UDESA-SUSCRIPCIONES DE SOFTWARE</t>
@@ -1049,144 +1027,144 @@
           <t>DATA &amp; GRAPHICS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="n"/>
-      <c r="K7" s="11" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="10" t="n"/>
+      <c r="K7" s="9" t="n"/>
       <c r="L7" s="10" t="n">
         <v>378.77</v>
       </c>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="11" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9" t="n"/>
       <c r="P7" s="10" t="n">
         <v>1385.88</v>
       </c>
-      <c r="Q7" s="11" t="n"/>
+      <c r="Q7" s="9" t="n"/>
       <c r="R7" s="10" t="n">
         <v>410.22</v>
       </c>
-      <c r="S7" s="11" t="n"/>
-      <c r="T7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="11" t="n"/>
-      <c r="V7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="11" t="n"/>
-      <c r="X7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="11" t="n"/>
-      <c r="Z7" s="11" t="n">
+      <c r="S7" s="9" t="n"/>
+      <c r="T7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="9" t="n"/>
+      <c r="V7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="9" t="n"/>
+      <c r="X7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="9" t="n"/>
+      <c r="Z7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="9" t="n">
         <v>25600</v>
       </c>
-      <c r="AB7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="11" t="n"/>
-      <c r="AD7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="11" t="n"/>
-      <c r="AF7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="12" t="n">
+      <c r="AB7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="9" t="n"/>
+      <c r="AD7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="9" t="n"/>
+      <c r="AF7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="11" t="n">
         <v>25600</v>
       </c>
-      <c r="AH7" s="12" t="n">
+      <c r="AH7" s="11" t="n">
         <v>2174.87</v>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>ADM-LICENCIAS DE PROGRAMAS</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Licencias de programas</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>412010904</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>Licencia Fortigate</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>LIBERTY NETWORKS EL SALVADOR / JM TELCOM</t>
         </is>
       </c>
-      <c r="I8" s="15" t="n"/>
+      <c r="I8" s="14" t="n"/>
       <c r="J8" s="15" t="n"/>
-      <c r="K8" s="15" t="n"/>
+      <c r="K8" s="14" t="n"/>
       <c r="L8" s="15" t="n"/>
-      <c r="M8" s="15" t="n"/>
+      <c r="M8" s="14" t="n"/>
       <c r="N8" s="15" t="n"/>
-      <c r="O8" s="15" t="n"/>
-      <c r="P8" s="19" t="n">
+      <c r="O8" s="14" t="n"/>
+      <c r="P8" s="15" t="n">
         <v>1895</v>
       </c>
-      <c r="Q8" s="15" t="n"/>
+      <c r="Q8" s="14" t="n"/>
       <c r="R8" s="15" t="n"/>
-      <c r="S8" s="15" t="n"/>
+      <c r="S8" s="14" t="n"/>
       <c r="T8" s="15" t="n"/>
-      <c r="U8" s="15" t="n"/>
+      <c r="U8" s="14" t="n"/>
       <c r="V8" s="15" t="n"/>
-      <c r="W8" s="15" t="n"/>
+      <c r="W8" s="14" t="n"/>
       <c r="X8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y8" s="15" t="n"/>
+      <c r="Y8" s="14" t="n"/>
       <c r="Z8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA8" s="15" t="n"/>
+      <c r="AA8" s="14" t="n"/>
       <c r="AB8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC8" s="15" t="n"/>
+      <c r="AC8" s="14" t="n"/>
       <c r="AD8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE8" s="15" t="n"/>
+      <c r="AE8" s="14" t="n"/>
       <c r="AF8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="17" t="n">
+      <c r="AG8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="16" t="n">
         <v>1895</v>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>ADM-COMUNICACIONES</t>
@@ -1258,171 +1236,171 @@
       <c r="S9" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="T9" s="11" t="n">
+      <c r="T9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="U9" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="V9" s="11" t="n">
+      <c r="V9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="X9" s="11" t="n">
+      <c r="X9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="Z9" s="11" t="n">
+      <c r="Z9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AA9" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="AB9" s="11" t="n">
+      <c r="AB9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AC9" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="AD9" s="11" t="n">
+      <c r="AD9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AE9" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="AF9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="12" t="n">
+      <c r="AF9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="11" t="n">
         <v>7200</v>
       </c>
-      <c r="AH9" s="12" t="n">
+      <c r="AH9" s="11" t="n">
         <v>3000</v>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>ADM-LICENCIAS DE PROGRAMAS</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Licencias de programas</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>412010904</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>Intelisis</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t>Grupo Octo</t>
         </is>
       </c>
-      <c r="I10" s="16" t="n">
+      <c r="I10" s="14" t="n">
         <v>4200</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="K10" s="16" t="n">
+      <c r="K10" s="14" t="n">
         <v>4200</v>
       </c>
-      <c r="L10" s="19" t="n">
+      <c r="L10" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="M10" s="16" t="n">
+      <c r="M10" s="14" t="n">
         <v>4200</v>
       </c>
-      <c r="N10" s="19" t="n">
+      <c r="N10" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="O10" s="16" t="n">
+      <c r="O10" s="14" t="n">
         <v>4200</v>
       </c>
-      <c r="P10" s="19" t="n">
+      <c r="P10" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="Q10" s="16" t="n">
+      <c r="Q10" s="14" t="n">
         <v>4200</v>
       </c>
-      <c r="R10" s="19" t="n">
+      <c r="R10" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="S10" s="16" t="n">
+      <c r="S10" s="14" t="n">
         <v>4200</v>
       </c>
-      <c r="T10" s="19" t="n">
+      <c r="T10" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="U10" s="16" t="n">
+      <c r="U10" s="14" t="n">
         <v>4200</v>
       </c>
       <c r="V10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W10" s="16" t="n">
+      <c r="W10" s="14" t="n">
         <v>4200</v>
       </c>
       <c r="X10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y10" s="16" t="n">
+      <c r="Y10" s="14" t="n">
         <v>4200</v>
       </c>
       <c r="Z10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA10" s="16" t="n">
+      <c r="AA10" s="14" t="n">
         <v>4200</v>
       </c>
       <c r="AB10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC10" s="16" t="n">
+      <c r="AC10" s="14" t="n">
         <v>4200</v>
       </c>
       <c r="AD10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE10" s="16" t="n">
+      <c r="AE10" s="14" t="n">
         <v>4200</v>
       </c>
       <c r="AF10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG10" s="17" t="n">
+      <c r="AG10" s="16" t="n">
         <v>50400</v>
       </c>
-      <c r="AH10" s="17" t="n">
+      <c r="AH10" s="16" t="n">
         <v>21000</v>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>UDESA-SERVICIOS DE TECNOLOGÍA</t>
@@ -1464,193 +1442,193 @@
       <c r="I11" s="9" t="n">
         <v>583</v>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="J11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>583</v>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="L11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="9" t="n">
         <v>583</v>
       </c>
-      <c r="N11" s="11" t="n">
+      <c r="N11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="9" t="n">
         <v>583</v>
       </c>
-      <c r="P11" s="11" t="n"/>
+      <c r="P11" s="10" t="n"/>
       <c r="Q11" s="9" t="n">
         <v>583</v>
       </c>
-      <c r="R11" s="11" t="n"/>
+      <c r="R11" s="10" t="n"/>
       <c r="S11" s="9" t="n">
         <v>583</v>
       </c>
-      <c r="T11" s="11" t="n">
+      <c r="T11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="U11" s="9" t="n">
         <v>583</v>
       </c>
-      <c r="V11" s="11" t="n">
+      <c r="V11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>583</v>
       </c>
-      <c r="X11" s="11" t="n">
+      <c r="X11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y11" s="9" t="n">
         <v>583</v>
       </c>
-      <c r="Z11" s="11" t="n">
+      <c r="Z11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AA11" s="9" t="n">
         <v>583</v>
       </c>
-      <c r="AB11" s="11" t="n">
+      <c r="AB11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AC11" s="9" t="n">
         <v>583</v>
       </c>
-      <c r="AD11" s="11" t="n">
+      <c r="AD11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AE11" s="9" t="n">
         <v>583</v>
       </c>
-      <c r="AF11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="12" t="n">
+      <c r="AF11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="11" t="n">
         <v>6996</v>
       </c>
-      <c r="AH11" s="20" t="n">
+      <c r="AH11" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>UDESA-SUSCRIPCIONES DE SOFTWARE</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Suscripciones y publicaciones</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>412010905</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>Azure</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t>DATA &amp; GRAPHICS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I12" s="16" t="n">
+      <c r="I12" s="14" t="n">
         <v>700</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="15" t="n">
         <v>895.84</v>
       </c>
-      <c r="K12" s="16" t="n">
+      <c r="K12" s="14" t="n">
         <v>700</v>
       </c>
       <c r="L12" s="15" t="n"/>
-      <c r="M12" s="16" t="n">
+      <c r="M12" s="14" t="n">
         <v>700</v>
       </c>
       <c r="N12" s="15" t="n"/>
-      <c r="O12" s="16" t="n">
+      <c r="O12" s="14" t="n">
         <v>700</v>
       </c>
-      <c r="P12" s="19" t="n">
+      <c r="P12" s="15" t="n">
         <v>1919.35</v>
       </c>
-      <c r="Q12" s="16" t="n">
+      <c r="Q12" s="14" t="n">
         <v>700</v>
       </c>
-      <c r="R12" s="19" t="n">
+      <c r="R12" s="15" t="n">
         <v>1890.51</v>
       </c>
-      <c r="S12" s="16" t="n">
+      <c r="S12" s="14" t="n">
         <v>700</v>
       </c>
       <c r="T12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U12" s="16" t="n">
+      <c r="U12" s="14" t="n">
         <v>700</v>
       </c>
       <c r="V12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W12" s="16" t="n">
+      <c r="W12" s="14" t="n">
         <v>700</v>
       </c>
       <c r="X12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y12" s="16" t="n">
+      <c r="Y12" s="14" t="n">
         <v>700</v>
       </c>
       <c r="Z12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA12" s="16" t="n">
+      <c r="AA12" s="14" t="n">
         <v>700</v>
       </c>
       <c r="AB12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC12" s="16" t="n">
+      <c r="AC12" s="14" t="n">
         <v>700</v>
       </c>
       <c r="AD12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE12" s="16" t="n">
+      <c r="AE12" s="14" t="n">
         <v>700</v>
       </c>
       <c r="AF12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG12" s="17" t="n">
+      <c r="AG12" s="16" t="n">
         <v>8400</v>
       </c>
-      <c r="AH12" s="17" t="n">
+      <c r="AH12" s="16" t="n">
         <v>4705.7</v>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>ADM-LICENCIAS DE PROGRAMAS</t>
@@ -1689,166 +1667,166 @@
           <t>LIBERTY NETWORKS EL SALVADOR, S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="11" t="n"/>
-      <c r="N13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="11" t="n"/>
-      <c r="P13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="11" t="n"/>
-      <c r="R13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="11" t="n"/>
-      <c r="T13" s="11" t="n">
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9" t="n"/>
+      <c r="L13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9" t="n"/>
+      <c r="N13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="9" t="n"/>
+      <c r="P13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="9" t="n"/>
+      <c r="R13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="9" t="n"/>
+      <c r="T13" s="10" t="n">
         <v>0</v>
       </c>
       <c r="U13" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="V13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="11" t="n"/>
-      <c r="X13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="11" t="n"/>
-      <c r="Z13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="11" t="n"/>
-      <c r="AB13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="11" t="n"/>
-      <c r="AD13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="11" t="n"/>
-      <c r="AF13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="12" t="n">
+      <c r="V13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9" t="n"/>
+      <c r="X13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="9" t="n"/>
+      <c r="Z13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9" t="n"/>
+      <c r="AB13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="9" t="n"/>
+      <c r="AD13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="9" t="n"/>
+      <c r="AF13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="AH13" s="20" t="n">
+      <c r="AH13" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>ADM-MANTENIMIENTO DE MOBILIARIO Y EQUIPO DE OFINA</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Mantenimiento de mobiliario y equipo de ofina</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>412010602</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>Mantenimiento informatico</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>CRUZ TERMINIO, LUIS DANIEL</t>
         </is>
       </c>
-      <c r="I14" s="15" t="n"/>
+      <c r="I14" s="14" t="n"/>
       <c r="J14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="15" t="n"/>
+      <c r="K14" s="14" t="n"/>
       <c r="L14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="16" t="n">
+      <c r="M14" s="14" t="n">
         <v>1900</v>
       </c>
-      <c r="N14" s="19" t="n">
+      <c r="N14" s="15" t="n">
         <v>1889</v>
       </c>
-      <c r="O14" s="15" t="n"/>
+      <c r="O14" s="14" t="n"/>
       <c r="P14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="15" t="n"/>
-      <c r="R14" s="19" t="n">
+      <c r="Q14" s="14" t="n"/>
+      <c r="R14" s="15" t="n">
         <v>1969</v>
       </c>
-      <c r="S14" s="16" t="n">
+      <c r="S14" s="14" t="n">
         <v>1900</v>
       </c>
       <c r="T14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U14" s="15" t="n"/>
+      <c r="U14" s="14" t="n"/>
       <c r="V14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="15" t="n"/>
+      <c r="W14" s="14" t="n"/>
       <c r="X14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y14" s="16" t="n">
+      <c r="Y14" s="14" t="n">
         <v>1900</v>
       </c>
       <c r="Z14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA14" s="15" t="n"/>
+      <c r="AA14" s="14" t="n"/>
       <c r="AB14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC14" s="15" t="n"/>
+      <c r="AC14" s="14" t="n"/>
       <c r="AD14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE14" s="16" t="n">
+      <c r="AE14" s="14" t="n">
         <v>1900</v>
       </c>
       <c r="AF14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG14" s="17" t="n">
+      <c r="AG14" s="16" t="n">
         <v>7600</v>
       </c>
-      <c r="AH14" s="17" t="n">
+      <c r="AH14" s="16" t="n">
         <v>3858</v>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>UDESA-SOPORTE TÉCNICO TERCERIZADO</t>
@@ -1920,169 +1898,169 @@
       <c r="S15" s="9" t="n">
         <v>800</v>
       </c>
-      <c r="T15" s="11" t="n">
+      <c r="T15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="U15" s="9" t="n">
         <v>800</v>
       </c>
-      <c r="V15" s="11" t="n">
+      <c r="V15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>800</v>
       </c>
-      <c r="X15" s="11" t="n">
+      <c r="X15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>800</v>
       </c>
-      <c r="Z15" s="11" t="n">
+      <c r="Z15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AA15" s="9" t="n">
         <v>800</v>
       </c>
-      <c r="AB15" s="11" t="n">
+      <c r="AB15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AC15" s="9" t="n">
         <v>800</v>
       </c>
-      <c r="AD15" s="11" t="n">
+      <c r="AD15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AE15" s="9" t="n">
         <v>800</v>
       </c>
-      <c r="AF15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="12" t="n">
+      <c r="AF15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="11" t="n">
         <v>9600</v>
       </c>
-      <c r="AH15" s="12" t="n">
+      <c r="AH15" s="11" t="n">
         <v>5610</v>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>UDESA-SOPORTE TÉCNICO TERCERIZADO</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B16" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Servicios Generales de Técnologia</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>412011220</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>Soporte visitas de campo</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>CANIZALEZ HERNANDEZ LUDWIN IVAN</t>
         </is>
       </c>
-      <c r="I16" s="16" t="n">
+      <c r="I16" s="14" t="n">
         <v>300</v>
       </c>
       <c r="J16" s="15" t="n"/>
-      <c r="K16" s="16" t="n">
+      <c r="K16" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="L16" s="19" t="n">
+      <c r="L16" s="15" t="n">
         <v>207.9</v>
       </c>
-      <c r="M16" s="16" t="n">
+      <c r="M16" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="N16" s="19" t="n">
+      <c r="N16" s="15" t="n">
         <v>600.6</v>
       </c>
-      <c r="O16" s="16" t="n">
+      <c r="O16" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="P16" s="19" t="n">
+      <c r="P16" s="15" t="n">
         <v>300.3</v>
       </c>
-      <c r="Q16" s="16" t="n">
+      <c r="Q16" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="R16" s="19" t="n">
+      <c r="R16" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="S16" s="16" t="n">
+      <c r="S16" s="14" t="n">
         <v>300</v>
       </c>
       <c r="T16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U16" s="16" t="n">
+      <c r="U16" s="14" t="n">
         <v>300</v>
       </c>
       <c r="V16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="16" t="n">
+      <c r="W16" s="14" t="n">
         <v>300</v>
       </c>
       <c r="X16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y16" s="16" t="n">
+      <c r="Y16" s="14" t="n">
         <v>300</v>
       </c>
       <c r="Z16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA16" s="16" t="n">
+      <c r="AA16" s="14" t="n">
         <v>300</v>
       </c>
       <c r="AB16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC16" s="16" t="n">
+      <c r="AC16" s="14" t="n">
         <v>300</v>
       </c>
       <c r="AD16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE16" s="16" t="n">
+      <c r="AE16" s="14" t="n">
         <v>300</v>
       </c>
       <c r="AF16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG16" s="17" t="n">
+      <c r="AG16" s="16" t="n">
         <v>3600</v>
       </c>
-      <c r="AH16" s="17" t="n">
+      <c r="AH16" s="16" t="n">
         <v>1208.8</v>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>ADM-MANTENIMIENTO DE MOBILIARIO Y EQUIPO DE OFINA</t>
@@ -2121,170 +2099,170 @@
           <t>CRUZ TERMINIO, LUIS DANIEL</t>
         </is>
       </c>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="11" t="n"/>
-      <c r="L17" s="11" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9" t="n"/>
+      <c r="L17" s="10" t="n"/>
       <c r="M17" s="9" t="n">
         <v>140</v>
       </c>
       <c r="N17" s="10" t="n">
         <v>140</v>
       </c>
-      <c r="O17" s="11" t="n"/>
-      <c r="P17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="11" t="n"/>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="9" t="n"/>
       <c r="R17" s="10" t="n">
         <v>185</v>
       </c>
       <c r="S17" s="9" t="n">
         <v>140</v>
       </c>
-      <c r="T17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="11" t="n"/>
-      <c r="V17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="11" t="n"/>
-      <c r="X17" s="11" t="n">
+      <c r="T17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="9" t="n"/>
+      <c r="X17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y17" s="9" t="n">
         <v>140</v>
       </c>
-      <c r="Z17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="11" t="n"/>
-      <c r="AB17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="11" t="n"/>
-      <c r="AD17" s="11" t="n">
+      <c r="Z17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="9" t="n"/>
+      <c r="AB17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="9" t="n"/>
+      <c r="AD17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AE17" s="9" t="n">
         <v>140</v>
       </c>
-      <c r="AF17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="12" t="n">
+      <c r="AF17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="11" t="n">
         <v>560</v>
       </c>
-      <c r="AH17" s="12" t="n">
+      <c r="AH17" s="11" t="n">
         <v>325</v>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>ADM-MANTENIMIENTO DE MOBILIARIO Y EQUIPO DE OFINA</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Mantenimiento de mobiliario y equipo de ofina</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>412010602</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>Mantenimiento UPS IB</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>CRUZ TERMINIO, LUIS DANIEL</t>
         </is>
       </c>
-      <c r="I18" s="15" t="n"/>
+      <c r="I18" s="14" t="n"/>
       <c r="J18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="15" t="n"/>
+      <c r="K18" s="14" t="n"/>
       <c r="L18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="16" t="n">
+      <c r="M18" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="N18" s="19" t="n">
+      <c r="N18" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="O18" s="15" t="n"/>
+      <c r="O18" s="14" t="n"/>
       <c r="P18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="15" t="n"/>
-      <c r="R18" s="19" t="n">
+      <c r="Q18" s="14" t="n"/>
+      <c r="R18" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="S18" s="16" t="n">
+      <c r="S18" s="14" t="n">
         <v>100</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U18" s="15" t="n"/>
+      <c r="U18" s="14" t="n"/>
       <c r="V18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W18" s="15" t="n"/>
+      <c r="W18" s="14" t="n"/>
       <c r="X18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y18" s="16" t="n">
+      <c r="Y18" s="14" t="n">
         <v>100</v>
       </c>
       <c r="Z18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA18" s="15" t="n"/>
+      <c r="AA18" s="14" t="n"/>
       <c r="AB18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC18" s="15" t="n"/>
+      <c r="AC18" s="14" t="n"/>
       <c r="AD18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE18" s="16" t="n">
+      <c r="AE18" s="14" t="n">
         <v>200</v>
       </c>
       <c r="AF18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG18" s="17" t="n">
+      <c r="AG18" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="AH18" s="17" t="n">
+      <c r="AH18" s="16" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>ADM-ACCESORIOS, PAQUETES Y PROGRAMAS</t>
@@ -2323,182 +2301,182 @@
           <t>CRUZ TERMINIO, LUIS DANIEL</t>
         </is>
       </c>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="11" t="n"/>
-      <c r="L19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="11" t="n"/>
-      <c r="P19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="11" t="n"/>
-      <c r="R19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="11" t="n"/>
-      <c r="T19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="11" t="n"/>
-      <c r="V19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" s="11" t="n"/>
-      <c r="X19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="11" t="n"/>
-      <c r="Z19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="11" t="n"/>
-      <c r="AB19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="11" t="n"/>
-      <c r="AD19" s="11" t="n">
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9" t="n"/>
+      <c r="L19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="9" t="n"/>
+      <c r="N19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="9" t="n"/>
+      <c r="P19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="9" t="n"/>
+      <c r="R19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="9" t="n"/>
+      <c r="T19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="9" t="n"/>
+      <c r="V19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="9" t="n"/>
+      <c r="X19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="9" t="n"/>
+      <c r="Z19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="9" t="n"/>
+      <c r="AB19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="9" t="n"/>
+      <c r="AD19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AE19" s="9" t="n">
         <v>750</v>
       </c>
-      <c r="AF19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="12" t="n">
+      <c r="AF19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="11" t="n">
         <v>750</v>
       </c>
-      <c r="AH19" s="20" t="n">
+      <c r="AH19" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>ADM-MANTENIMIENTO DE MOBILIARIO Y EQUIPO DE OFINA</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
+      <c r="B20" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Mantenimiento de mobiliario y equipo de ofina</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>412010602</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>Mantenimiento impresores RICOH</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="H20" s="13" t="inlineStr">
         <is>
           <t>RICOH EL SALVADOR, S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I20" s="16" t="n">
+      <c r="I20" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="J20" s="19" t="n">
+      <c r="J20" s="15" t="n">
         <v>72</v>
       </c>
-      <c r="K20" s="16" t="n">
+      <c r="K20" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="L20" s="19" t="n">
+      <c r="L20" s="15" t="n">
         <v>216</v>
       </c>
-      <c r="M20" s="16" t="n">
+      <c r="M20" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="N20" s="19" t="n">
+      <c r="N20" s="15" t="n">
         <v>354.56</v>
       </c>
-      <c r="O20" s="16" t="n">
+      <c r="O20" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="P20" s="19" t="n">
+      <c r="P20" s="15" t="n">
         <v>394.25</v>
       </c>
-      <c r="Q20" s="16" t="n">
+      <c r="Q20" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="R20" s="19" t="n">
+      <c r="R20" s="15" t="n">
         <v>322.25</v>
       </c>
-      <c r="S20" s="16" t="n">
+      <c r="S20" s="14" t="n">
         <v>150</v>
       </c>
       <c r="T20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U20" s="16" t="n">
+      <c r="U20" s="14" t="n">
         <v>150</v>
       </c>
       <c r="V20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W20" s="16" t="n">
+      <c r="W20" s="14" t="n">
         <v>150</v>
       </c>
       <c r="X20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y20" s="16" t="n">
+      <c r="Y20" s="14" t="n">
         <v>150</v>
       </c>
       <c r="Z20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA20" s="16" t="n">
+      <c r="AA20" s="14" t="n">
         <v>150</v>
       </c>
       <c r="AB20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC20" s="16" t="n">
+      <c r="AC20" s="14" t="n">
         <v>150</v>
       </c>
       <c r="AD20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE20" s="16" t="n">
+      <c r="AE20" s="14" t="n">
         <v>150</v>
       </c>
       <c r="AF20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG20" s="17" t="n">
+      <c r="AG20" s="16" t="n">
         <v>1800</v>
       </c>
-      <c r="AH20" s="17" t="n">
+      <c r="AH20" s="16" t="n">
         <v>1359.06</v>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1">
+    <row r="21" ht="15" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
           <t>ADM-CONSUMIBLES FOTOCOPIADORA</t>
@@ -2540,171 +2518,171 @@
       <c r="I21" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="J21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="11" t="n"/>
-      <c r="L21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="11" t="n"/>
-      <c r="N21" s="11" t="n"/>
+      <c r="J21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9" t="n"/>
+      <c r="L21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="9" t="n"/>
+      <c r="N21" s="10" t="n"/>
       <c r="O21" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="P21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="11" t="n"/>
-      <c r="R21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="11" t="n"/>
-      <c r="T21" s="11" t="n">
+      <c r="P21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="9" t="n"/>
+      <c r="R21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="9" t="n"/>
+      <c r="T21" s="10" t="n">
         <v>0</v>
       </c>
       <c r="U21" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="V21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="11" t="n"/>
-      <c r="X21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="11" t="n"/>
-      <c r="Z21" s="11" t="n">
+      <c r="V21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="9" t="n"/>
+      <c r="X21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="9" t="n"/>
+      <c r="Z21" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AA21" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="AB21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="11" t="n"/>
-      <c r="AD21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="11" t="n"/>
-      <c r="AF21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="12" t="n">
+      <c r="AB21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="9" t="n"/>
+      <c r="AD21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="9" t="n"/>
+      <c r="AF21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="11" t="n">
         <v>1600</v>
       </c>
-      <c r="AH21" s="20" t="n">
+      <c r="AH21" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>ADM-CONSUMIBLES FOTOCOPIADORA</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
+      <c r="B22" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Consumibles y accesorios equipos de oficina</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>412010906</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>Toner impresores</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t>RICOH EL SALVADOR, S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I22" s="16" t="n">
+      <c r="I22" s="14" t="n">
         <v>550</v>
       </c>
       <c r="J22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="15" t="n"/>
+      <c r="K22" s="14" t="n"/>
       <c r="L22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="16" t="n">
+      <c r="M22" s="14" t="n">
         <v>550</v>
       </c>
-      <c r="N22" s="19" t="n">
+      <c r="N22" s="15" t="n">
         <v>522</v>
       </c>
-      <c r="O22" s="15" t="n"/>
+      <c r="O22" s="14" t="n"/>
       <c r="P22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="16" t="n">
+      <c r="Q22" s="14" t="n">
         <v>550</v>
       </c>
       <c r="R22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S22" s="15" t="n"/>
+      <c r="S22" s="14" t="n"/>
       <c r="T22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U22" s="16" t="n">
+      <c r="U22" s="14" t="n">
         <v>550</v>
       </c>
       <c r="V22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W22" s="15" t="n"/>
+      <c r="W22" s="14" t="n"/>
       <c r="X22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y22" s="16" t="n">
+      <c r="Y22" s="14" t="n">
         <v>550</v>
       </c>
       <c r="Z22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA22" s="15" t="n"/>
+      <c r="AA22" s="14" t="n"/>
       <c r="AB22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC22" s="16" t="n">
+      <c r="AC22" s="14" t="n">
         <v>550</v>
       </c>
       <c r="AD22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE22" s="15" t="n"/>
+      <c r="AE22" s="14" t="n"/>
       <c r="AF22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG22" s="17" t="n">
+      <c r="AG22" s="16" t="n">
         <v>3300</v>
       </c>
-      <c r="AH22" s="17" t="n">
+      <c r="AH22" s="16" t="n">
         <v>522</v>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
+    <row r="23" ht="15" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
           <t>ADM-MANTENIMIENTO DE PLANTA TELEFÓNICA</t>
@@ -2749,12 +2727,12 @@
       <c r="J23" s="10" t="n">
         <v>335.16</v>
       </c>
-      <c r="K23" s="11" t="n"/>
-      <c r="L23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="11" t="n"/>
-      <c r="N23" s="11" t="n">
+      <c r="K23" s="9" t="n"/>
+      <c r="L23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="9" t="n"/>
+      <c r="N23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="9" t="n">
@@ -2763,168 +2741,168 @@
       <c r="P23" s="10" t="n">
         <v>335.16</v>
       </c>
-      <c r="Q23" s="11" t="n"/>
-      <c r="R23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="11" t="n"/>
-      <c r="T23" s="11" t="n">
+      <c r="Q23" s="9" t="n"/>
+      <c r="R23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="9" t="n"/>
+      <c r="T23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="U23" s="9" t="n">
         <v>380</v>
       </c>
-      <c r="V23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" s="11" t="n"/>
-      <c r="X23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="11" t="n"/>
-      <c r="Z23" s="11" t="n">
+      <c r="V23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="9" t="n"/>
+      <c r="X23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="9" t="n"/>
+      <c r="Z23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AA23" s="9" t="n">
         <v>380</v>
       </c>
-      <c r="AB23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="11" t="n"/>
-      <c r="AD23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="11" t="n"/>
-      <c r="AF23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="12" t="n">
+      <c r="AB23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="9" t="n"/>
+      <c r="AD23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="9" t="n"/>
+      <c r="AF23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="11" t="n">
         <v>1520</v>
       </c>
-      <c r="AH23" s="12" t="n">
+      <c r="AH23" s="11" t="n">
         <v>670.3200000000001</v>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>ADM-LICENCIAS DE PROGRAMAS</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
+      <c r="B24" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Finanzas</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Licencias de programas</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>412010904</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>Laserfiche</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>RICOH EL SALVADOR, S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I24" s="16" t="n">
+      <c r="I24" s="14" t="n">
         <v>525.1</v>
       </c>
       <c r="J24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="16" t="n">
+      <c r="K24" s="14" t="n">
         <v>525.1</v>
       </c>
-      <c r="L24" s="19" t="n">
+      <c r="L24" s="15" t="n">
         <v>2480.35</v>
       </c>
-      <c r="M24" s="16" t="n">
+      <c r="M24" s="14" t="n">
         <v>525.1</v>
       </c>
       <c r="N24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="16" t="n">
+      <c r="O24" s="14" t="n">
         <v>525.1</v>
       </c>
       <c r="P24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" s="16" t="n">
+      <c r="Q24" s="14" t="n">
         <v>525.1</v>
       </c>
       <c r="R24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="16" t="n">
+      <c r="S24" s="14" t="n">
         <v>525.1</v>
       </c>
       <c r="T24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U24" s="16" t="n">
+      <c r="U24" s="14" t="n">
         <v>525.1</v>
       </c>
       <c r="V24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W24" s="16" t="n">
+      <c r="W24" s="14" t="n">
         <v>525.1</v>
       </c>
       <c r="X24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y24" s="16" t="n">
+      <c r="Y24" s="14" t="n">
         <v>525.1</v>
       </c>
       <c r="Z24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA24" s="16" t="n">
+      <c r="AA24" s="14" t="n">
         <v>525.1</v>
       </c>
       <c r="AB24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC24" s="16" t="n">
+      <c r="AC24" s="14" t="n">
         <v>525.1</v>
       </c>
       <c r="AD24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE24" s="16" t="n">
+      <c r="AE24" s="14" t="n">
         <v>525.1</v>
       </c>
       <c r="AF24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG24" s="17" t="n">
+      <c r="AG24" s="16" t="n">
         <v>6301.200000000002</v>
       </c>
-      <c r="AH24" s="17" t="n">
+      <c r="AH24" s="16" t="n">
         <v>2480.35</v>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1">
+    <row r="25" ht="15" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
           <t>ADM-LICENCIAS DE PROGRAMAS</t>
@@ -2966,175 +2944,175 @@
       <c r="I25" s="9" t="n">
         <v>350</v>
       </c>
-      <c r="J25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="11" t="n"/>
-      <c r="L25" s="11" t="n">
+      <c r="J25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="9" t="n"/>
+      <c r="L25" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M25" s="9" t="n">
         <v>350</v>
       </c>
-      <c r="N25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="11" t="n"/>
-      <c r="P25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="11" t="n"/>
-      <c r="R25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="11" t="n"/>
-      <c r="T25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="11" t="n"/>
-      <c r="V25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" s="11" t="n"/>
-      <c r="X25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="11" t="n"/>
-      <c r="Z25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="11" t="n"/>
-      <c r="AB25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="11" t="n"/>
-      <c r="AD25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" s="11" t="n"/>
-      <c r="AF25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" s="12" t="n">
+      <c r="N25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="9" t="n"/>
+      <c r="P25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="9" t="n"/>
+      <c r="R25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="9" t="n"/>
+      <c r="T25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="9" t="n"/>
+      <c r="V25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="9" t="n"/>
+      <c r="X25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="9" t="n"/>
+      <c r="Z25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="9" t="n"/>
+      <c r="AB25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="9" t="n"/>
+      <c r="AD25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="9" t="n"/>
+      <c r="AF25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="11" t="n">
         <v>700</v>
       </c>
-      <c r="AH25" s="20" t="n">
+      <c r="AH25" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>UDESA-SUSCRIPCIONES DE SOFTWARE</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
+      <c r="B26" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>Suscripciones y publicaciones</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>412010905</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>GLPi (Inventario IT)</t>
         </is>
       </c>
-      <c r="H26" s="14" t="inlineStr">
+      <c r="H26" s="13" t="inlineStr">
         <is>
           <t>TECLIB</t>
         </is>
       </c>
-      <c r="I26" s="16" t="n">
+      <c r="I26" s="14" t="n">
         <v>45</v>
       </c>
       <c r="J26" s="15" t="n"/>
-      <c r="K26" s="16" t="n">
+      <c r="K26" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="L26" s="19" t="n">
+      <c r="L26" s="15" t="n">
         <v>112.9</v>
       </c>
-      <c r="M26" s="16" t="n">
+      <c r="M26" s="14" t="n">
         <v>45</v>
       </c>
       <c r="N26" s="15" t="n"/>
-      <c r="O26" s="16" t="n">
+      <c r="O26" s="14" t="n">
         <v>45</v>
       </c>
       <c r="P26" s="15" t="n"/>
-      <c r="Q26" s="16" t="n">
+      <c r="Q26" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="R26" s="19" t="n">
+      <c r="R26" s="15" t="n">
         <v>111.35</v>
       </c>
-      <c r="S26" s="16" t="n">
+      <c r="S26" s="14" t="n">
         <v>45</v>
       </c>
       <c r="T26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U26" s="16" t="n">
+      <c r="U26" s="14" t="n">
         <v>45</v>
       </c>
       <c r="V26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W26" s="16" t="n">
+      <c r="W26" s="14" t="n">
         <v>45</v>
       </c>
       <c r="X26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y26" s="16" t="n">
+      <c r="Y26" s="14" t="n">
         <v>45</v>
       </c>
       <c r="Z26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA26" s="16" t="n">
+      <c r="AA26" s="14" t="n">
         <v>45</v>
       </c>
       <c r="AB26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC26" s="16" t="n">
+      <c r="AC26" s="14" t="n">
         <v>45</v>
       </c>
       <c r="AD26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE26" s="16" t="n">
+      <c r="AE26" s="14" t="n">
         <v>45</v>
       </c>
       <c r="AF26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG26" s="17" t="n">
+      <c r="AG26" s="16" t="n">
         <v>540</v>
       </c>
-      <c r="AH26" s="17" t="n">
+      <c r="AH26" s="16" t="n">
         <v>224.25</v>
       </c>
     </row>
-    <row r="27" ht="16" customHeight="1">
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
           <t>ADM-LICENCIAS DE PROGRAMAS</t>
@@ -3173,178 +3151,178 @@
           <t>Cleverbridge GmbH</t>
         </is>
       </c>
-      <c r="I27" s="11" t="n"/>
-      <c r="J27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="11" t="n"/>
-      <c r="L27" s="11" t="n">
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="9" t="n"/>
+      <c r="L27" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="N27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="11" t="n"/>
-      <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="11" t="n"/>
-      <c r="R27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="11" t="n"/>
-      <c r="T27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="11" t="n"/>
-      <c r="V27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" s="11" t="n"/>
-      <c r="X27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="11" t="n"/>
-      <c r="Z27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="11" t="n"/>
-      <c r="AB27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="11" t="n"/>
-      <c r="AD27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="11" t="n"/>
-      <c r="AF27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="12" t="n">
+      <c r="N27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="9" t="n"/>
+      <c r="P27" s="10" t="n"/>
+      <c r="Q27" s="9" t="n"/>
+      <c r="R27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="9" t="n"/>
+      <c r="T27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="9" t="n"/>
+      <c r="V27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="9" t="n"/>
+      <c r="X27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="9" t="n"/>
+      <c r="Z27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="9" t="n"/>
+      <c r="AB27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="9" t="n"/>
+      <c r="AD27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="9" t="n"/>
+      <c r="AF27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="11" t="n">
         <v>120</v>
       </c>
-      <c r="AH27" s="20" t="n">
+      <c r="AH27" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>ADM-ACCESORIOS, PAQUETES Y PROGRAMAS</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G28" s="14" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>Compras de insumos, repuestos, etc</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr">
+      <c r="H28" s="13" t="inlineStr">
         <is>
           <t>CRUZ TERMINIO, LUIS DANIEL</t>
         </is>
       </c>
-      <c r="I28" s="16" t="n">
+      <c r="I28" s="14" t="n">
         <v>500</v>
       </c>
       <c r="J28" s="15" t="n"/>
-      <c r="K28" s="16" t="n">
+      <c r="K28" s="14" t="n">
         <v>500</v>
       </c>
-      <c r="L28" s="19" t="n">
+      <c r="L28" s="15" t="n">
         <v>787</v>
       </c>
-      <c r="M28" s="16" t="n">
+      <c r="M28" s="14" t="n">
         <v>500</v>
       </c>
-      <c r="N28" s="19" t="n">
+      <c r="N28" s="15" t="n">
         <v>1215.56</v>
       </c>
-      <c r="O28" s="16" t="n">
+      <c r="O28" s="14" t="n">
         <v>500</v>
       </c>
-      <c r="P28" s="19" t="n">
+      <c r="P28" s="15" t="n">
         <v>887</v>
       </c>
-      <c r="Q28" s="16" t="n">
+      <c r="Q28" s="14" t="n">
         <v>500</v>
       </c>
-      <c r="R28" s="19" t="n">
+      <c r="R28" s="15" t="n">
         <v>718</v>
       </c>
-      <c r="S28" s="16" t="n">
+      <c r="S28" s="14" t="n">
         <v>500</v>
       </c>
       <c r="T28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U28" s="16" t="n">
+      <c r="U28" s="14" t="n">
         <v>500</v>
       </c>
       <c r="V28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W28" s="16" t="n">
+      <c r="W28" s="14" t="n">
         <v>500</v>
       </c>
       <c r="X28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y28" s="16" t="n">
+      <c r="Y28" s="14" t="n">
         <v>500</v>
       </c>
       <c r="Z28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA28" s="16" t="n">
+      <c r="AA28" s="14" t="n">
         <v>500</v>
       </c>
       <c r="AB28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC28" s="16" t="n">
+      <c r="AC28" s="14" t="n">
         <v>500</v>
       </c>
       <c r="AD28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE28" s="16" t="n">
+      <c r="AE28" s="14" t="n">
         <v>500</v>
       </c>
       <c r="AF28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG28" s="17" t="n">
+      <c r="AG28" s="16" t="n">
         <v>6000</v>
       </c>
-      <c r="AH28" s="17" t="n">
+      <c r="AH28" s="16" t="n">
         <v>3607.56</v>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1">
+    <row r="29" ht="15" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
           <t>ADM-ACCESORIOS, PAQUETES Y PROGRAMAS</t>
@@ -3383,160 +3361,160 @@
           <t>GRUPO OCTO S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
-      <c r="N29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="11" t="n"/>
-      <c r="P29" s="11" t="n"/>
-      <c r="Q29" s="11" t="n"/>
-      <c r="R29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="11" t="n"/>
-      <c r="T29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="11" t="n"/>
-      <c r="V29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" s="11" t="n"/>
-      <c r="X29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="11" t="n"/>
-      <c r="Z29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="11" t="n"/>
-      <c r="AB29" s="11" t="n">
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="9" t="n"/>
+      <c r="L29" s="10" t="n"/>
+      <c r="M29" s="9" t="n"/>
+      <c r="N29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="9" t="n"/>
+      <c r="P29" s="10" t="n"/>
+      <c r="Q29" s="9" t="n"/>
+      <c r="R29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="9" t="n"/>
+      <c r="T29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="9" t="n"/>
+      <c r="V29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="9" t="n"/>
+      <c r="X29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="9" t="n"/>
+      <c r="Z29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="9" t="n"/>
+      <c r="AB29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AC29" s="9" t="n">
         <v>500</v>
       </c>
-      <c r="AD29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="11" t="n"/>
-      <c r="AF29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="12" t="n">
+      <c r="AD29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="9" t="n"/>
+      <c r="AF29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="AH29" s="20" t="n">
+      <c r="AH29" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>ADM-ACCESORIOS, PAQUETES Y PROGRAMAS</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>AISA Administración</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>Microsoft 365 IB</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="H30" s="13" t="inlineStr">
         <is>
           <t>DATA &amp; GRAPHICS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I30" s="15" t="n"/>
+      <c r="I30" s="14" t="n"/>
       <c r="J30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="15" t="n"/>
+      <c r="K30" s="14" t="n"/>
       <c r="L30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="15" t="n"/>
+      <c r="M30" s="14" t="n"/>
       <c r="N30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="15" t="n"/>
+      <c r="O30" s="14" t="n"/>
       <c r="P30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="15" t="n"/>
+      <c r="Q30" s="14" t="n"/>
       <c r="R30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="15" t="n"/>
+      <c r="S30" s="14" t="n"/>
       <c r="T30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U30" s="15" t="n"/>
+      <c r="U30" s="14" t="n"/>
       <c r="V30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="15" t="n"/>
+      <c r="W30" s="14" t="n"/>
       <c r="X30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y30" s="15" t="n"/>
+      <c r="Y30" s="14" t="n"/>
       <c r="Z30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA30" s="16" t="n">
+      <c r="AA30" s="14" t="n">
         <v>1641.5</v>
       </c>
       <c r="AB30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC30" s="16" t="n">
+      <c r="AC30" s="14" t="n">
         <v>1641.5</v>
       </c>
       <c r="AD30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE30" s="16" t="n">
+      <c r="AE30" s="14" t="n">
         <v>1407</v>
       </c>
       <c r="AF30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG30" s="17" t="n">
+      <c r="AG30" s="16" t="n">
         <v>4690</v>
       </c>
-      <c r="AH30" s="18" t="n">
+      <c r="AH30" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1">
+    <row r="31" ht="15" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
           <t>ADM-MANTENIMIENTO DE MOBILIARIO Y EQUIPO DE OFINA</t>
@@ -3575,178 +3553,178 @@
           <t>SERVICIOS TECNOLOGICOS E INFORMATICOS S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I31" s="11" t="n"/>
-      <c r="J31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="11" t="n"/>
-      <c r="L31" s="11" t="n">
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="9" t="n"/>
+      <c r="L31" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M31" s="9" t="n">
         <v>640</v>
       </c>
-      <c r="N31" s="11" t="n"/>
-      <c r="O31" s="11" t="n"/>
-      <c r="P31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="11" t="n"/>
-      <c r="R31" s="11" t="n">
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="9" t="n"/>
+      <c r="P31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="9" t="n"/>
+      <c r="R31" s="10" t="n">
         <v>0</v>
       </c>
       <c r="S31" s="9" t="n">
         <v>640</v>
       </c>
-      <c r="T31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="11" t="n"/>
-      <c r="V31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" s="11" t="n"/>
-      <c r="X31" s="11" t="n">
+      <c r="T31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="9" t="n"/>
+      <c r="V31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="9" t="n"/>
+      <c r="X31" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y31" s="9" t="n">
         <v>640</v>
       </c>
-      <c r="Z31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="11" t="n"/>
-      <c r="AB31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="11" t="n"/>
-      <c r="AD31" s="11" t="n">
+      <c r="Z31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="9" t="n"/>
+      <c r="AB31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="9" t="n"/>
+      <c r="AD31" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AE31" s="9" t="n">
         <v>640</v>
       </c>
-      <c r="AF31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" s="12" t="n">
+      <c r="AF31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="11" t="n">
         <v>2560</v>
       </c>
-      <c r="AH31" s="20" t="n">
+      <c r="AH31" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>ADM-MANTENIMIENTO DE MOBILIARIO Y EQUIPO DE OFINA</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>AISA Administración</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>Mantenimiento de mobiliario y equipo de ofina</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>412010602</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
+      <c r="G32" s="13" t="inlineStr">
         <is>
           <t>Tecnico destacado KNK</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="H32" s="13" t="inlineStr">
         <is>
           <t>KNK</t>
         </is>
       </c>
-      <c r="I32" s="16" t="n">
+      <c r="I32" s="14" t="n">
         <v>105</v>
       </c>
       <c r="J32" s="15" t="n"/>
-      <c r="K32" s="16" t="n">
+      <c r="K32" s="14" t="n">
         <v>105</v>
       </c>
       <c r="L32" s="15" t="n"/>
-      <c r="M32" s="16" t="n">
+      <c r="M32" s="14" t="n">
         <v>105</v>
       </c>
       <c r="N32" s="15" t="n"/>
-      <c r="O32" s="16" t="n">
+      <c r="O32" s="14" t="n">
         <v>105</v>
       </c>
       <c r="P32" s="15" t="n"/>
-      <c r="Q32" s="16" t="n">
+      <c r="Q32" s="14" t="n">
         <v>105</v>
       </c>
       <c r="R32" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S32" s="16" t="n">
+      <c r="S32" s="14" t="n">
         <v>105</v>
       </c>
       <c r="T32" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U32" s="16" t="n">
+      <c r="U32" s="14" t="n">
         <v>105</v>
       </c>
       <c r="V32" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W32" s="16" t="n">
+      <c r="W32" s="14" t="n">
         <v>105</v>
       </c>
       <c r="X32" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y32" s="16" t="n">
+      <c r="Y32" s="14" t="n">
         <v>105</v>
       </c>
       <c r="Z32" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA32" s="16" t="n">
+      <c r="AA32" s="14" t="n">
         <v>105</v>
       </c>
       <c r="AB32" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC32" s="16" t="n">
+      <c r="AC32" s="14" t="n">
         <v>105</v>
       </c>
       <c r="AD32" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE32" s="16" t="n">
+      <c r="AE32" s="14" t="n">
         <v>105</v>
       </c>
       <c r="AF32" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG32" s="17" t="n">
+      <c r="AG32" s="16" t="n">
         <v>1260</v>
       </c>
-      <c r="AH32" s="18" t="n">
+      <c r="AH32" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="16" customHeight="1">
+    <row r="33" ht="15" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
           <t>ADM-MANTENIMIENTO DE MOBILIARIO Y EQUIPO DE OFINA</t>
@@ -3788,197 +3766,197 @@
       <c r="I33" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="J33" s="11" t="n">
+      <c r="J33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="L33" s="11" t="n">
+      <c r="L33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M33" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="N33" s="11" t="n">
+      <c r="N33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="P33" s="11" t="n">
+      <c r="P33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="R33" s="11" t="n">
+      <c r="R33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="S33" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="T33" s="11" t="n">
+      <c r="T33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="U33" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="V33" s="11" t="n">
+      <c r="V33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="X33" s="11" t="n">
+      <c r="X33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y33" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Z33" s="11" t="n">
+      <c r="Z33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AA33" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="AB33" s="11" t="n">
+      <c r="AB33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AC33" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="AD33" s="11" t="n">
+      <c r="AD33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AE33" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="AF33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" s="12" t="n">
+      <c r="AF33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="11" t="n">
         <v>600</v>
       </c>
-      <c r="AH33" s="20" t="n">
+      <c r="AH33" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>ADM-ACCESORIOS, PAQUETES Y PROGRAMAS</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
+      <c r="B34" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>AISA Administración</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G34" s="13" t="inlineStr">
         <is>
           <t>Compras de insumos, repuestos, etc</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H34" s="13" t="inlineStr">
         <is>
           <t>(-)</t>
         </is>
       </c>
-      <c r="I34" s="16" t="n">
+      <c r="I34" s="14" t="n">
         <v>100</v>
       </c>
       <c r="J34" s="15" t="n"/>
-      <c r="K34" s="16" t="n">
+      <c r="K34" s="14" t="n">
         <v>100</v>
       </c>
       <c r="L34" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="M34" s="16" t="n">
+      <c r="M34" s="14" t="n">
         <v>100</v>
       </c>
       <c r="N34" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="16" t="n">
+      <c r="O34" s="14" t="n">
         <v>100</v>
       </c>
       <c r="P34" s="15" t="n"/>
-      <c r="Q34" s="16" t="n">
+      <c r="Q34" s="14" t="n">
         <v>100</v>
       </c>
       <c r="R34" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S34" s="16" t="n">
+      <c r="S34" s="14" t="n">
         <v>100</v>
       </c>
       <c r="T34" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U34" s="16" t="n">
+      <c r="U34" s="14" t="n">
         <v>100</v>
       </c>
       <c r="V34" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W34" s="16" t="n">
+      <c r="W34" s="14" t="n">
         <v>100</v>
       </c>
       <c r="X34" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y34" s="16" t="n">
+      <c r="Y34" s="14" t="n">
         <v>100</v>
       </c>
       <c r="Z34" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA34" s="16" t="n">
+      <c r="AA34" s="14" t="n">
         <v>100</v>
       </c>
       <c r="AB34" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC34" s="16" t="n">
+      <c r="AC34" s="14" t="n">
         <v>100</v>
       </c>
       <c r="AD34" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE34" s="16" t="n">
+      <c r="AE34" s="14" t="n">
         <v>100</v>
       </c>
       <c r="AF34" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG34" s="17" t="n">
+      <c r="AG34" s="16" t="n">
         <v>1200</v>
       </c>
-      <c r="AH34" s="18" t="n">
+      <c r="AH34" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1">
+    <row r="35" ht="15" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
           <t>ADM-ACCESORIOS, PAQUETES Y PROGRAMAS</t>
@@ -4020,157 +3998,157 @@
       <c r="I35" s="9" t="n">
         <v>4000</v>
       </c>
-      <c r="J35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="11" t="n"/>
-      <c r="L35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="11" t="n"/>
-      <c r="N35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="11" t="n"/>
-      <c r="P35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="11" t="n"/>
-      <c r="R35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="11" t="n"/>
-      <c r="T35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="11" t="n"/>
-      <c r="V35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="11" t="n"/>
-      <c r="X35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="11" t="n"/>
-      <c r="Z35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="11" t="n"/>
-      <c r="AB35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="11" t="n"/>
-      <c r="AD35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="11" t="n"/>
-      <c r="AF35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="12" t="n">
+      <c r="J35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="9" t="n"/>
+      <c r="P35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="9" t="n"/>
+      <c r="R35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="9" t="n"/>
+      <c r="T35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="9" t="n"/>
+      <c r="V35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="9" t="n"/>
+      <c r="X35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="9" t="n"/>
+      <c r="Z35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="9" t="n"/>
+      <c r="AB35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="9" t="n"/>
+      <c r="AD35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="9" t="n"/>
+      <c r="AF35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="11" t="n">
         <v>4000</v>
       </c>
-      <c r="AH35" s="20" t="n">
+      <c r="AH35" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>UDESA-SUSCRIPCIONES DE SOFTWARE</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n">
+      <c r="B36" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>Suscripciones y publicaciones</t>
         </is>
       </c>
-      <c r="F36" s="14" t="inlineStr">
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>412010905</t>
         </is>
       </c>
-      <c r="G36" s="14" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
         <is>
           <t>Policom Studio (2) Sala Panda y sala 2</t>
         </is>
       </c>
-      <c r="H36" s="14" t="inlineStr">
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t>Poly/HP</t>
         </is>
       </c>
-      <c r="I36" s="16" t="n">
+      <c r="I36" s="14" t="n">
         <v>1600</v>
       </c>
       <c r="J36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="K36" s="15" t="n"/>
+      <c r="K36" s="14" t="n"/>
       <c r="L36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="15" t="n"/>
+      <c r="M36" s="14" t="n"/>
       <c r="N36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="15" t="n"/>
+      <c r="O36" s="14" t="n"/>
       <c r="P36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" s="15" t="n"/>
+      <c r="Q36" s="14" t="n"/>
       <c r="R36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S36" s="15" t="n"/>
+      <c r="S36" s="14" t="n"/>
       <c r="T36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U36" s="15" t="n"/>
+      <c r="U36" s="14" t="n"/>
       <c r="V36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="15" t="n"/>
+      <c r="W36" s="14" t="n"/>
       <c r="X36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y36" s="15" t="n"/>
+      <c r="Y36" s="14" t="n"/>
       <c r="Z36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA36" s="15" t="n"/>
+      <c r="AA36" s="14" t="n"/>
       <c r="AB36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC36" s="15" t="n"/>
+      <c r="AC36" s="14" t="n"/>
       <c r="AD36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE36" s="15" t="n"/>
+      <c r="AE36" s="14" t="n"/>
       <c r="AF36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="17" t="n">
+      <c r="AG36" s="16" t="n">
         <v>1600</v>
       </c>
-      <c r="AH36" s="18" t="n">
+      <c r="AH36" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="37" ht="16" customHeight="1">
+    <row r="37" ht="15" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
           <t>UDESA-SUSCRIPCIONES DE SOFTWARE</t>
@@ -4209,178 +4187,178 @@
           <t>DATA &amp; GRAPHICS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I37" s="11" t="n"/>
-      <c r="J37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="11" t="n"/>
-      <c r="L37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="11" t="n"/>
-      <c r="N37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="11" t="n"/>
-      <c r="P37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="11" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="9" t="n"/>
+      <c r="L37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="9" t="n"/>
+      <c r="P37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="9" t="n"/>
       <c r="R37" s="10" t="n">
         <v>490</v>
       </c>
-      <c r="S37" s="11" t="n"/>
-      <c r="T37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="11" t="n"/>
-      <c r="V37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="11" t="n"/>
-      <c r="X37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="11" t="n"/>
-      <c r="Z37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="11" t="n"/>
-      <c r="AB37" s="11" t="n">
+      <c r="S37" s="9" t="n"/>
+      <c r="T37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="9" t="n"/>
+      <c r="V37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="9" t="n"/>
+      <c r="X37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="9" t="n"/>
+      <c r="Z37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="9" t="n"/>
+      <c r="AB37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AC37" s="9" t="n">
         <v>2600</v>
       </c>
-      <c r="AD37" s="11" t="n"/>
+      <c r="AD37" s="10" t="n"/>
       <c r="AE37" s="9" t="n">
         <v>2145</v>
       </c>
-      <c r="AF37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" s="12" t="n">
+      <c r="AF37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="11" t="n">
         <v>4745</v>
       </c>
-      <c r="AH37" s="12" t="n">
+      <c r="AH37" s="11" t="n">
         <v>490</v>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>UDESA-SERVICIOS DE TECNOLOGÍA</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
+      <c r="B38" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>Servicios Generales de Técnologia</t>
         </is>
       </c>
-      <c r="F38" s="14" t="inlineStr">
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>412011220</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G38" s="13" t="inlineStr">
         <is>
           <t>Zoom Hablemos</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr">
+      <c r="H38" s="13" t="inlineStr">
         <is>
           <t>ZOOM VIDEO COMMUNICATIONS INC.</t>
         </is>
       </c>
-      <c r="I38" s="16" t="n">
+      <c r="I38" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="J38" s="19" t="n">
+      <c r="J38" s="15" t="n">
         <v>106.19</v>
       </c>
-      <c r="K38" s="16" t="n">
+      <c r="K38" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="L38" s="19" t="n">
+      <c r="L38" s="15" t="n">
         <v>106.2</v>
       </c>
-      <c r="M38" s="16" t="n">
+      <c r="M38" s="14" t="n">
         <v>25</v>
       </c>
       <c r="N38" s="15" t="n"/>
-      <c r="O38" s="16" t="n">
+      <c r="O38" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="P38" s="19" t="n">
+      <c r="P38" s="15" t="n">
         <v>148.67</v>
       </c>
-      <c r="Q38" s="16" t="n">
+      <c r="Q38" s="14" t="n">
         <v>25</v>
       </c>
       <c r="R38" s="15" t="n"/>
-      <c r="S38" s="16" t="n">
+      <c r="S38" s="14" t="n">
         <v>25</v>
       </c>
       <c r="T38" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U38" s="16" t="n">
+      <c r="U38" s="14" t="n">
         <v>25</v>
       </c>
       <c r="V38" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W38" s="16" t="n">
+      <c r="W38" s="14" t="n">
         <v>25</v>
       </c>
       <c r="X38" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y38" s="16" t="n">
+      <c r="Y38" s="14" t="n">
         <v>25</v>
       </c>
       <c r="Z38" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA38" s="16" t="n">
+      <c r="AA38" s="14" t="n">
         <v>25</v>
       </c>
       <c r="AB38" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC38" s="16" t="n">
+      <c r="AC38" s="14" t="n">
         <v>25</v>
       </c>
       <c r="AD38" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE38" s="16" t="n">
+      <c r="AE38" s="14" t="n">
         <v>25</v>
       </c>
       <c r="AF38" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG38" s="17" t="n">
+      <c r="AG38" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="AH38" s="17" t="n">
+      <c r="AH38" s="16" t="n">
         <v>361.0599999999999</v>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1">
+    <row r="39" ht="15" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
           <t>UDESA-SERVICIOS DE TECNOLOGÍA</t>
@@ -4422,25 +4400,25 @@
       <c r="I39" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="J39" s="11" t="n">
+      <c r="J39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="L39" s="11" t="n">
+      <c r="L39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M39" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="N39" s="11" t="n">
+      <c r="N39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="P39" s="11" t="n"/>
+      <c r="P39" s="10" t="n"/>
       <c r="Q39" s="9" t="n">
         <v>400</v>
       </c>
@@ -4450,145 +4428,145 @@
       <c r="S39" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="T39" s="11" t="n">
+      <c r="T39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="U39" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="V39" s="11" t="n">
+      <c r="V39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="X39" s="11" t="n">
+      <c r="X39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y39" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="Z39" s="11" t="n">
+      <c r="Z39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AA39" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="AB39" s="11" t="n">
+      <c r="AB39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AC39" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="AD39" s="11" t="n">
+      <c r="AD39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AE39" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="AF39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" s="12" t="n">
+      <c r="AF39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="11" t="n">
         <v>4800</v>
       </c>
-      <c r="AH39" s="12" t="n">
+      <c r="AH39" s="11" t="n">
         <v>349.28</v>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>UDESA-SERVICIOS DE TECNOLOGÍA</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n">
+      <c r="B40" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D40" s="14" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>Servicios Generales de Técnologia</t>
         </is>
       </c>
-      <c r="F40" s="14" t="inlineStr">
+      <c r="F40" s="13" t="inlineStr">
         <is>
           <t>412011220</t>
         </is>
       </c>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G40" s="13" t="inlineStr">
         <is>
           <t>Servicios de consumo de aws</t>
         </is>
       </c>
-      <c r="H40" s="14" t="inlineStr">
+      <c r="H40" s="13" t="inlineStr">
         <is>
           <t>Amazon Web Services</t>
         </is>
       </c>
-      <c r="I40" s="15" t="n"/>
+      <c r="I40" s="14" t="n"/>
       <c r="J40" s="15" t="n"/>
-      <c r="K40" s="15" t="n"/>
-      <c r="L40" s="19" t="n">
+      <c r="K40" s="14" t="n"/>
+      <c r="L40" s="15" t="n">
         <v>769.92</v>
       </c>
-      <c r="M40" s="15" t="n"/>
-      <c r="N40" s="19" t="n">
+      <c r="M40" s="14" t="n"/>
+      <c r="N40" s="15" t="n">
         <v>343.79</v>
       </c>
-      <c r="O40" s="15" t="n"/>
+      <c r="O40" s="14" t="n"/>
       <c r="P40" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" s="15" t="n"/>
+      <c r="Q40" s="14" t="n"/>
       <c r="R40" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="S40" s="15" t="n"/>
+      <c r="S40" s="14" t="n"/>
       <c r="T40" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U40" s="15" t="n"/>
+      <c r="U40" s="14" t="n"/>
       <c r="V40" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="W40" s="15" t="n"/>
+      <c r="W40" s="14" t="n"/>
       <c r="X40" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="Y40" s="15" t="n"/>
+      <c r="Y40" s="14" t="n"/>
       <c r="Z40" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA40" s="15" t="n"/>
+      <c r="AA40" s="14" t="n"/>
       <c r="AB40" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AC40" s="15" t="n"/>
+      <c r="AC40" s="14" t="n"/>
       <c r="AD40" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AE40" s="15" t="n"/>
+      <c r="AE40" s="14" t="n"/>
       <c r="AF40" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AG40" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" s="17" t="n">
+      <c r="AG40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" s="16" t="n">
         <v>1113.71</v>
       </c>
     </row>
-    <row r="41" ht="16" customHeight="1">
+    <row r="41" ht="15" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
@@ -4660,153 +4638,153 @@
       <c r="S41" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="T41" s="11" t="n">
+      <c r="T41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="U41" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="V41" s="11" t="n">
+      <c r="V41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="X41" s="11" t="n">
+      <c r="X41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y41" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="Z41" s="11" t="n">
+      <c r="Z41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AA41" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="AB41" s="11" t="n">
+      <c r="AB41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AC41" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="AD41" s="11" t="n">
+      <c r="AD41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AE41" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="AF41" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" s="12" t="n">
+      <c r="AF41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="11" t="n">
         <v>1440</v>
       </c>
-      <c r="AH41" s="12" t="n">
+      <c r="AH41" s="11" t="n">
         <v>580</v>
       </c>
     </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="13" t="inlineStr">
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
+      <c r="B42" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>Tecnología</t>
         </is>
       </c>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F42" s="14" t="inlineStr">
+      <c r="F42" s="13" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G42" s="14" t="inlineStr">
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t>Licencia de team Heygen</t>
         </is>
       </c>
-      <c r="H42" s="14" t="inlineStr">
+      <c r="H42" s="13" t="inlineStr">
         <is>
           <t>HEYGEN TECHNOLOGY INC</t>
         </is>
       </c>
-      <c r="I42" s="16" t="n">
+      <c r="I42" s="14" t="n">
         <v>99</v>
       </c>
       <c r="J42" s="15" t="n"/>
-      <c r="K42" s="16" t="n">
+      <c r="K42" s="14" t="n">
         <v>99</v>
       </c>
-      <c r="L42" s="19" t="n">
+      <c r="L42" s="15" t="n">
         <v>36.25</v>
       </c>
-      <c r="M42" s="16" t="n">
+      <c r="M42" s="14" t="n">
         <v>99</v>
       </c>
-      <c r="N42" s="19" t="n">
+      <c r="N42" s="15" t="n">
         <v>36.25</v>
       </c>
-      <c r="O42" s="16" t="n">
+      <c r="O42" s="14" t="n">
         <v>99</v>
       </c>
       <c r="P42" s="15" t="n"/>
-      <c r="Q42" s="16" t="n">
+      <c r="Q42" s="14" t="n">
         <v>84</v>
       </c>
-      <c r="R42" s="19" t="n">
+      <c r="R42" s="15" t="n">
         <v>72.5</v>
       </c>
-      <c r="S42" s="16" t="n">
+      <c r="S42" s="14" t="n">
         <v>84</v>
       </c>
       <c r="T42" s="15" t="n"/>
-      <c r="U42" s="16" t="n">
+      <c r="U42" s="14" t="n">
         <v>84</v>
       </c>
       <c r="V42" s="15" t="n"/>
-      <c r="W42" s="16" t="n">
+      <c r="W42" s="14" t="n">
         <v>84</v>
       </c>
       <c r="X42" s="15" t="n"/>
-      <c r="Y42" s="16" t="n">
+      <c r="Y42" s="14" t="n">
         <v>84</v>
       </c>
       <c r="Z42" s="15" t="n"/>
-      <c r="AA42" s="16" t="n">
+      <c r="AA42" s="14" t="n">
         <v>84</v>
       </c>
       <c r="AB42" s="15" t="n"/>
-      <c r="AC42" s="16" t="n">
+      <c r="AC42" s="14" t="n">
         <v>84</v>
       </c>
       <c r="AD42" s="15" t="n"/>
-      <c r="AE42" s="15" t="n">
+      <c r="AE42" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AF42" s="15" t="n"/>
-      <c r="AG42" s="17" t="n">
+      <c r="AG42" s="16" t="n">
         <v>984</v>
       </c>
-      <c r="AH42" s="17" t="n">
+      <c r="AH42" s="16" t="n">
         <v>145</v>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1">
+    <row r="43" ht="15" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
@@ -4848,153 +4826,153 @@
       <c r="I43" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="J43" s="11" t="n"/>
+      <c r="J43" s="10" t="n"/>
       <c r="K43" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="L43" s="11" t="n"/>
+      <c r="L43" s="10" t="n"/>
       <c r="M43" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="N43" s="11" t="n"/>
+      <c r="N43" s="10" t="n"/>
       <c r="O43" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="P43" s="11" t="n"/>
+      <c r="P43" s="10" t="n"/>
       <c r="Q43" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="R43" s="11" t="n"/>
+      <c r="R43" s="10" t="n"/>
       <c r="S43" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="T43" s="11" t="n"/>
+      <c r="T43" s="10" t="n"/>
       <c r="U43" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="V43" s="11" t="n"/>
+      <c r="V43" s="10" t="n"/>
       <c r="W43" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="X43" s="11" t="n"/>
+      <c r="X43" s="10" t="n"/>
       <c r="Y43" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Z43" s="11" t="n"/>
+      <c r="Z43" s="10" t="n"/>
       <c r="AA43" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="AB43" s="11" t="n"/>
+      <c r="AB43" s="10" t="n"/>
       <c r="AC43" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="AD43" s="11" t="n"/>
+      <c r="AD43" s="10" t="n"/>
       <c r="AE43" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="AF43" s="11" t="n"/>
-      <c r="AG43" s="12" t="n">
+      <c r="AF43" s="10" t="n"/>
+      <c r="AG43" s="11" t="n">
         <v>600</v>
       </c>
-      <c r="AH43" s="20" t="n">
+      <c r="AH43" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="13" t="inlineStr">
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B44" s="14" t="n">
+      <c r="B44" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="C44" s="14" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>Tecnología</t>
         </is>
       </c>
-      <c r="D44" s="14" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F44" s="14" t="inlineStr">
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G44" s="14" t="inlineStr">
+      <c r="G44" s="13" t="inlineStr">
         <is>
           <t>Google AI Studio</t>
         </is>
       </c>
-      <c r="H44" s="14" t="inlineStr">
+      <c r="H44" s="13" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="I44" s="16" t="n">
+      <c r="I44" s="14" t="n">
         <v>20</v>
       </c>
       <c r="J44" s="15" t="n"/>
-      <c r="K44" s="16" t="n">
+      <c r="K44" s="14" t="n">
         <v>20</v>
       </c>
       <c r="L44" s="15" t="n"/>
-      <c r="M44" s="16" t="n">
+      <c r="M44" s="14" t="n">
         <v>20</v>
       </c>
       <c r="N44" s="15" t="n"/>
-      <c r="O44" s="16" t="n">
+      <c r="O44" s="14" t="n">
         <v>20</v>
       </c>
       <c r="P44" s="15" t="n"/>
-      <c r="Q44" s="16" t="n">
+      <c r="Q44" s="14" t="n">
         <v>20</v>
       </c>
       <c r="R44" s="15" t="n"/>
-      <c r="S44" s="16" t="n">
+      <c r="S44" s="14" t="n">
         <v>20</v>
       </c>
       <c r="T44" s="15" t="n"/>
-      <c r="U44" s="16" t="n">
+      <c r="U44" s="14" t="n">
         <v>20</v>
       </c>
       <c r="V44" s="15" t="n"/>
-      <c r="W44" s="16" t="n">
+      <c r="W44" s="14" t="n">
         <v>20</v>
       </c>
       <c r="X44" s="15" t="n"/>
-      <c r="Y44" s="16" t="n">
+      <c r="Y44" s="14" t="n">
         <v>20</v>
       </c>
       <c r="Z44" s="15" t="n"/>
-      <c r="AA44" s="16" t="n">
+      <c r="AA44" s="14" t="n">
         <v>20</v>
       </c>
       <c r="AB44" s="15" t="n"/>
-      <c r="AC44" s="16" t="n">
+      <c r="AC44" s="14" t="n">
         <v>20</v>
       </c>
       <c r="AD44" s="15" t="n"/>
-      <c r="AE44" s="15" t="n">
+      <c r="AE44" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AF44" s="15" t="n"/>
-      <c r="AG44" s="17" t="n">
+      <c r="AG44" s="16" t="n">
         <v>220</v>
       </c>
-      <c r="AH44" s="18" t="n">
+      <c r="AH44" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="16" customHeight="1">
+    <row r="45" ht="15" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
@@ -5036,153 +5014,153 @@
       <c r="I45" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="J45" s="11" t="n"/>
+      <c r="J45" s="10" t="n"/>
       <c r="K45" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="L45" s="11" t="n"/>
+      <c r="L45" s="10" t="n"/>
       <c r="M45" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="N45" s="11" t="n"/>
+      <c r="N45" s="10" t="n"/>
       <c r="O45" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="P45" s="11" t="n"/>
+      <c r="P45" s="10" t="n"/>
       <c r="Q45" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="R45" s="11" t="n"/>
+      <c r="R45" s="10" t="n"/>
       <c r="S45" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="T45" s="11" t="n"/>
+      <c r="T45" s="10" t="n"/>
       <c r="U45" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="V45" s="11" t="n"/>
+      <c r="V45" s="10" t="n"/>
       <c r="W45" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="X45" s="11" t="n"/>
+      <c r="X45" s="10" t="n"/>
       <c r="Y45" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="Z45" s="11" t="n"/>
+      <c r="Z45" s="10" t="n"/>
       <c r="AA45" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="AB45" s="11" t="n"/>
+      <c r="AB45" s="10" t="n"/>
       <c r="AC45" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="AD45" s="11" t="n"/>
+      <c r="AD45" s="10" t="n"/>
       <c r="AE45" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="AF45" s="11" t="n"/>
-      <c r="AG45" s="12" t="n">
+      <c r="AF45" s="10" t="n"/>
+      <c r="AG45" s="11" t="n">
         <v>1500</v>
       </c>
-      <c r="AH45" s="20" t="n">
+      <c r="AH45" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B46" s="14" t="n">
+      <c r="B46" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>Tecnología</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F46" s="14" t="inlineStr">
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G46" s="14" t="inlineStr">
+      <c r="G46" s="13" t="inlineStr">
         <is>
           <t>Licencias de Copilot personales</t>
         </is>
       </c>
-      <c r="H46" s="14" t="inlineStr">
+      <c r="H46" s="13" t="inlineStr">
         <is>
           <t>DATA &amp; GRAPHICS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I46" s="16" t="n">
+      <c r="I46" s="14" t="n">
         <v>550</v>
       </c>
       <c r="J46" s="15" t="n"/>
-      <c r="K46" s="16" t="n">
+      <c r="K46" s="14" t="n">
         <v>550</v>
       </c>
       <c r="L46" s="15" t="n"/>
-      <c r="M46" s="16" t="n">
+      <c r="M46" s="14" t="n">
         <v>550</v>
       </c>
       <c r="N46" s="15" t="n"/>
-      <c r="O46" s="16" t="n">
+      <c r="O46" s="14" t="n">
         <v>550</v>
       </c>
       <c r="P46" s="15" t="n"/>
-      <c r="Q46" s="16" t="n">
+      <c r="Q46" s="14" t="n">
         <v>550</v>
       </c>
       <c r="R46" s="15" t="n"/>
-      <c r="S46" s="16" t="n">
+      <c r="S46" s="14" t="n">
         <v>550</v>
       </c>
       <c r="T46" s="15" t="n"/>
-      <c r="U46" s="16" t="n">
+      <c r="U46" s="14" t="n">
         <v>550</v>
       </c>
       <c r="V46" s="15" t="n"/>
-      <c r="W46" s="16" t="n">
+      <c r="W46" s="14" t="n">
         <v>550</v>
       </c>
       <c r="X46" s="15" t="n"/>
-      <c r="Y46" s="16" t="n">
+      <c r="Y46" s="14" t="n">
         <v>550</v>
       </c>
       <c r="Z46" s="15" t="n"/>
-      <c r="AA46" s="16" t="n">
+      <c r="AA46" s="14" t="n">
         <v>550</v>
       </c>
       <c r="AB46" s="15" t="n"/>
-      <c r="AC46" s="16" t="n">
+      <c r="AC46" s="14" t="n">
         <v>550</v>
       </c>
       <c r="AD46" s="15" t="n"/>
-      <c r="AE46" s="16" t="n">
+      <c r="AE46" s="14" t="n">
         <v>550</v>
       </c>
       <c r="AF46" s="15" t="n"/>
-      <c r="AG46" s="17" t="n">
+      <c r="AG46" s="16" t="n">
         <v>6600</v>
       </c>
-      <c r="AH46" s="18" t="n">
+      <c r="AH46" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="16" customHeight="1">
+    <row r="47" ht="15" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
@@ -5221,16 +5199,16 @@
           <t>ANTHROPIC, PBC</t>
         </is>
       </c>
-      <c r="I47" s="11" t="n"/>
-      <c r="J47" s="11" t="n"/>
-      <c r="K47" s="11" t="n"/>
-      <c r="L47" s="11" t="n"/>
-      <c r="M47" s="11" t="n"/>
-      <c r="N47" s="11" t="n"/>
-      <c r="O47" s="11" t="n"/>
-      <c r="P47" s="11" t="n"/>
-      <c r="Q47" s="11" t="n"/>
-      <c r="R47" s="11" t="n"/>
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="10" t="n"/>
+      <c r="K47" s="9" t="n"/>
+      <c r="L47" s="10" t="n"/>
+      <c r="M47" s="9" t="n"/>
+      <c r="N47" s="10" t="n"/>
+      <c r="O47" s="9" t="n"/>
+      <c r="P47" s="10" t="n"/>
+      <c r="Q47" s="9" t="n"/>
+      <c r="R47" s="10" t="n"/>
       <c r="S47" s="9" t="n">
         <v>100</v>
       </c>
@@ -5240,129 +5218,129 @@
       <c r="U47" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="V47" s="11" t="n"/>
+      <c r="V47" s="10" t="n"/>
       <c r="W47" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="X47" s="11" t="n"/>
+      <c r="X47" s="10" t="n"/>
       <c r="Y47" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="Z47" s="11" t="n"/>
+      <c r="Z47" s="10" t="n"/>
       <c r="AA47" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="AB47" s="11" t="n"/>
+      <c r="AB47" s="10" t="n"/>
       <c r="AC47" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="AD47" s="11" t="n"/>
+      <c r="AD47" s="10" t="n"/>
       <c r="AE47" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="AF47" s="11" t="n"/>
-      <c r="AG47" s="12" t="n">
+      <c r="AF47" s="10" t="n"/>
+      <c r="AG47" s="11" t="n">
         <v>700</v>
       </c>
-      <c r="AH47" s="12" t="n">
+      <c r="AH47" s="11" t="n">
         <v>125</v>
       </c>
     </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B48" s="14" t="n">
+      <c r="B48" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="C48" s="14" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>Tecnología</t>
         </is>
       </c>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F48" s="14" t="inlineStr">
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G48" s="14" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr">
         <is>
           <t>Licencia Copilot Studio</t>
         </is>
       </c>
-      <c r="H48" s="14" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr">
         <is>
           <t>DATA &amp; GRAPHICS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I48" s="16" t="n">
+      <c r="I48" s="14" t="n">
         <v>200</v>
       </c>
       <c r="J48" s="15" t="n"/>
-      <c r="K48" s="16" t="n">
+      <c r="K48" s="14" t="n">
         <v>200</v>
       </c>
       <c r="L48" s="15" t="n"/>
-      <c r="M48" s="16" t="n">
+      <c r="M48" s="14" t="n">
         <v>200</v>
       </c>
       <c r="N48" s="15" t="n"/>
-      <c r="O48" s="16" t="n">
+      <c r="O48" s="14" t="n">
         <v>200</v>
       </c>
       <c r="P48" s="15" t="n"/>
-      <c r="Q48" s="16" t="n">
+      <c r="Q48" s="14" t="n">
         <v>200</v>
       </c>
       <c r="R48" s="15" t="n"/>
-      <c r="S48" s="16" t="n">
+      <c r="S48" s="14" t="n">
         <v>200</v>
       </c>
       <c r="T48" s="15" t="n"/>
-      <c r="U48" s="16" t="n">
+      <c r="U48" s="14" t="n">
         <v>200</v>
       </c>
       <c r="V48" s="15" t="n"/>
-      <c r="W48" s="16" t="n">
+      <c r="W48" s="14" t="n">
         <v>200</v>
       </c>
       <c r="X48" s="15" t="n"/>
-      <c r="Y48" s="16" t="n">
+      <c r="Y48" s="14" t="n">
         <v>200</v>
       </c>
       <c r="Z48" s="15" t="n"/>
-      <c r="AA48" s="16" t="n">
+      <c r="AA48" s="14" t="n">
         <v>200</v>
       </c>
       <c r="AB48" s="15" t="n"/>
-      <c r="AC48" s="16" t="n">
+      <c r="AC48" s="14" t="n">
         <v>200</v>
       </c>
       <c r="AD48" s="15" t="n"/>
-      <c r="AE48" s="16" t="n">
+      <c r="AE48" s="14" t="n">
         <v>200</v>
       </c>
       <c r="AF48" s="15" t="n"/>
-      <c r="AG48" s="17" t="n">
+      <c r="AG48" s="16" t="n">
         <v>2400</v>
       </c>
-      <c r="AH48" s="18" t="n">
+      <c r="AH48" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="49" ht="16" customHeight="1">
+    <row r="49" ht="15" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
@@ -5401,114 +5379,114 @@
           <t>LINKEDIN IRELAND UNLIMITED COMPANY</t>
         </is>
       </c>
-      <c r="I49" s="11" t="n"/>
-      <c r="J49" s="11" t="n"/>
-      <c r="K49" s="11" t="n"/>
+      <c r="I49" s="9" t="n"/>
+      <c r="J49" s="10" t="n"/>
+      <c r="K49" s="9" t="n"/>
       <c r="L49" s="10" t="n">
         <v>212.49</v>
       </c>
-      <c r="M49" s="11" t="n"/>
-      <c r="N49" s="11" t="n"/>
-      <c r="O49" s="11" t="n"/>
-      <c r="P49" s="11" t="n"/>
-      <c r="Q49" s="11" t="n"/>
-      <c r="R49" s="11" t="n"/>
-      <c r="S49" s="11" t="n"/>
-      <c r="T49" s="11" t="n"/>
-      <c r="U49" s="11" t="n"/>
-      <c r="V49" s="11" t="n"/>
-      <c r="W49" s="11" t="n"/>
-      <c r="X49" s="11" t="n"/>
-      <c r="Y49" s="11" t="n"/>
-      <c r="Z49" s="11" t="n"/>
-      <c r="AA49" s="11" t="n"/>
-      <c r="AB49" s="11" t="n"/>
-      <c r="AC49" s="11" t="n"/>
-      <c r="AD49" s="11" t="n"/>
-      <c r="AE49" s="11" t="n"/>
-      <c r="AF49" s="11" t="n"/>
-      <c r="AG49" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="12" t="n">
+      <c r="M49" s="9" t="n"/>
+      <c r="N49" s="10" t="n"/>
+      <c r="O49" s="9" t="n"/>
+      <c r="P49" s="10" t="n"/>
+      <c r="Q49" s="9" t="n"/>
+      <c r="R49" s="10" t="n"/>
+      <c r="S49" s="9" t="n"/>
+      <c r="T49" s="10" t="n"/>
+      <c r="U49" s="9" t="n"/>
+      <c r="V49" s="10" t="n"/>
+      <c r="W49" s="9" t="n"/>
+      <c r="X49" s="10" t="n"/>
+      <c r="Y49" s="9" t="n"/>
+      <c r="Z49" s="10" t="n"/>
+      <c r="AA49" s="9" t="n"/>
+      <c r="AB49" s="10" t="n"/>
+      <c r="AC49" s="9" t="n"/>
+      <c r="AD49" s="10" t="n"/>
+      <c r="AE49" s="9" t="n"/>
+      <c r="AF49" s="10" t="n"/>
+      <c r="AG49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="11" t="n">
         <v>212.49</v>
       </c>
     </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B50" s="14" t="n">
+      <c r="B50" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="C50" s="14" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>Tecnología</t>
         </is>
       </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
         <is>
           <t>Power Automate licencia</t>
         </is>
       </c>
-      <c r="H50" s="14" t="inlineStr">
+      <c r="H50" s="13" t="inlineStr">
         <is>
           <t>DATA &amp; GRAPHICS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I50" s="15" t="n"/>
+      <c r="I50" s="14" t="n"/>
       <c r="J50" s="15" t="n"/>
-      <c r="K50" s="15" t="n"/>
+      <c r="K50" s="14" t="n"/>
       <c r="L50" s="15" t="n"/>
-      <c r="M50" s="15" t="n"/>
+      <c r="M50" s="14" t="n"/>
       <c r="N50" s="15" t="n"/>
-      <c r="O50" s="15" t="n"/>
+      <c r="O50" s="14" t="n"/>
       <c r="P50" s="15" t="n"/>
-      <c r="Q50" s="15" t="n"/>
-      <c r="R50" s="19" t="n">
+      <c r="Q50" s="14" t="n"/>
+      <c r="R50" s="15" t="n">
         <v>178.78</v>
       </c>
-      <c r="S50" s="15" t="n"/>
+      <c r="S50" s="14" t="n"/>
       <c r="T50" s="15" t="n"/>
-      <c r="U50" s="15" t="n"/>
+      <c r="U50" s="14" t="n"/>
       <c r="V50" s="15" t="n"/>
-      <c r="W50" s="15" t="n"/>
+      <c r="W50" s="14" t="n"/>
       <c r="X50" s="15" t="n"/>
-      <c r="Y50" s="15" t="n"/>
+      <c r="Y50" s="14" t="n"/>
       <c r="Z50" s="15" t="n"/>
-      <c r="AA50" s="15" t="n">
+      <c r="AA50" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AB50" s="15" t="n"/>
-      <c r="AC50" s="15" t="n"/>
+      <c r="AC50" s="14" t="n"/>
       <c r="AD50" s="15" t="n"/>
-      <c r="AE50" s="15" t="n"/>
+      <c r="AE50" s="14" t="n"/>
       <c r="AF50" s="15" t="n"/>
-      <c r="AG50" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="17" t="n">
+      <c r="AG50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="16" t="n">
         <v>178.78</v>
       </c>
     </row>
-    <row r="51" ht="16" customHeight="1">
+    <row r="51" ht="15" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
           <t>ADM-Licencias de programas</t>
@@ -5547,185 +5525,185 @@
           <t>JMTELCOM, JESUS MARTINEZ Y ASOCIADOS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I51" s="11" t="n"/>
-      <c r="J51" s="11" t="n"/>
-      <c r="K51" s="11" t="n"/>
-      <c r="L51" s="11" t="n"/>
-      <c r="M51" s="11" t="n"/>
-      <c r="N51" s="11" t="n"/>
-      <c r="O51" s="11" t="n"/>
+      <c r="I51" s="9" t="n"/>
+      <c r="J51" s="10" t="n"/>
+      <c r="K51" s="9" t="n"/>
+      <c r="L51" s="10" t="n"/>
+      <c r="M51" s="9" t="n"/>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="9" t="n"/>
       <c r="P51" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="Q51" s="11" t="n"/>
-      <c r="R51" s="11" t="n"/>
-      <c r="S51" s="11" t="n"/>
-      <c r="T51" s="11" t="n"/>
-      <c r="U51" s="11" t="n"/>
-      <c r="V51" s="11" t="n"/>
-      <c r="W51" s="11" t="n"/>
-      <c r="X51" s="11" t="n"/>
-      <c r="Y51" s="11" t="n"/>
-      <c r="Z51" s="11" t="n"/>
-      <c r="AA51" s="11" t="n"/>
-      <c r="AB51" s="11" t="n"/>
-      <c r="AC51" s="11" t="n"/>
-      <c r="AD51" s="11" t="n"/>
-      <c r="AE51" s="11" t="n"/>
-      <c r="AF51" s="11" t="n"/>
-      <c r="AG51" s="20" t="n"/>
-      <c r="AH51" s="12" t="n">
+      <c r="Q51" s="9" t="n"/>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="9" t="n"/>
+      <c r="T51" s="10" t="n"/>
+      <c r="U51" s="9" t="n"/>
+      <c r="V51" s="10" t="n"/>
+      <c r="W51" s="9" t="n"/>
+      <c r="X51" s="10" t="n"/>
+      <c r="Y51" s="9" t="n"/>
+      <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="9" t="n"/>
+      <c r="AB51" s="10" t="n"/>
+      <c r="AC51" s="9" t="n"/>
+      <c r="AD51" s="10" t="n"/>
+      <c r="AE51" s="9" t="n"/>
+      <c r="AF51" s="10" t="n"/>
+      <c r="AG51" s="11" t="n"/>
+      <c r="AH51" s="11" t="n">
         <v>5000</v>
       </c>
     </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="13" t="inlineStr">
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>UDESA-Servicios de Tecnología</t>
         </is>
       </c>
-      <c r="B52" s="14" t="n">
+      <c r="B52" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="E52" s="14" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>INSTALACION DE EQUIPOS FORTINET EN LEASING</t>
         </is>
       </c>
-      <c r="F52" s="14" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>412011220</t>
         </is>
       </c>
-      <c r="G52" s="14" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t>INTALACION DE EQUOPOS /  DTE-0900</t>
         </is>
       </c>
-      <c r="H52" s="14" t="inlineStr">
+      <c r="H52" s="13" t="inlineStr">
         <is>
           <t>JMTELCOM, JESUS MARTINEZ Y ASOCIADOS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I52" s="15" t="n"/>
+      <c r="I52" s="14" t="n"/>
       <c r="J52" s="15" t="n"/>
-      <c r="K52" s="15" t="n"/>
+      <c r="K52" s="14" t="n"/>
       <c r="L52" s="15" t="n"/>
-      <c r="M52" s="15" t="n"/>
+      <c r="M52" s="14" t="n"/>
       <c r="N52" s="15" t="n"/>
-      <c r="O52" s="15" t="n"/>
-      <c r="P52" s="19" t="n">
+      <c r="O52" s="14" t="n"/>
+      <c r="P52" s="15" t="n">
         <v>1895</v>
       </c>
-      <c r="Q52" s="15" t="n"/>
+      <c r="Q52" s="14" t="n"/>
       <c r="R52" s="15" t="n"/>
-      <c r="S52" s="15" t="n"/>
+      <c r="S52" s="14" t="n"/>
       <c r="T52" s="15" t="n"/>
-      <c r="U52" s="15" t="n"/>
+      <c r="U52" s="14" t="n"/>
       <c r="V52" s="15" t="n"/>
-      <c r="W52" s="15" t="n"/>
+      <c r="W52" s="14" t="n"/>
       <c r="X52" s="15" t="n"/>
-      <c r="Y52" s="15" t="n"/>
+      <c r="Y52" s="14" t="n"/>
       <c r="Z52" s="15" t="n"/>
-      <c r="AA52" s="15" t="n"/>
+      <c r="AA52" s="14" t="n"/>
       <c r="AB52" s="15" t="n"/>
-      <c r="AC52" s="15" t="n"/>
+      <c r="AC52" s="14" t="n"/>
       <c r="AD52" s="15" t="n"/>
-      <c r="AE52" s="15" t="n"/>
+      <c r="AE52" s="14" t="n"/>
       <c r="AF52" s="15" t="n"/>
-      <c r="AG52" s="18" t="n"/>
-      <c r="AH52" s="17" t="n">
+      <c r="AG52" s="16" t="n"/>
+      <c r="AH52" s="16" t="n">
         <v>1895</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="21" t="inlineStr">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>TOTAL GENERAL</t>
         </is>
       </c>
-      <c r="I53" s="22" t="n">
+      <c r="I53" s="18" t="n">
         <v>20527.1</v>
       </c>
-      <c r="J53" s="22" t="n">
+      <c r="J53" s="18" t="n">
         <v>22376.19</v>
       </c>
-      <c r="K53" s="22" t="n">
+      <c r="K53" s="18" t="n">
         <v>13247.1</v>
       </c>
-      <c r="L53" s="22" t="n">
+      <c r="L53" s="18" t="n">
         <v>10585.29</v>
       </c>
-      <c r="M53" s="22" t="n">
+      <c r="M53" s="18" t="n">
         <v>17047.1</v>
       </c>
-      <c r="N53" s="22" t="n">
+      <c r="N53" s="18" t="n">
         <v>10541.76</v>
       </c>
-      <c r="O53" s="22" t="n">
+      <c r="O53" s="18" t="n">
         <v>14027.1</v>
       </c>
-      <c r="P53" s="22" t="n">
+      <c r="P53" s="18" t="n">
         <v>12640.61</v>
       </c>
-      <c r="Q53" s="22" t="n">
+      <c r="Q53" s="18" t="n">
         <v>13782.1</v>
       </c>
-      <c r="R53" s="22" t="n">
+      <c r="R53" s="18" t="n">
         <v>13928.05</v>
       </c>
-      <c r="S53" s="22" t="n">
+      <c r="S53" s="18" t="n">
         <v>16112.1</v>
       </c>
-      <c r="T53" s="22" t="n">
+      <c r="T53" s="18" t="n">
         <v>3625</v>
       </c>
-      <c r="U53" s="22" t="n">
+      <c r="U53" s="18" t="n">
         <v>14962.1</v>
       </c>
-      <c r="V53" s="22" t="n"/>
-      <c r="W53" s="22" t="n">
+      <c r="V53" s="18" t="n"/>
+      <c r="W53" s="18" t="n">
         <v>13332.1</v>
       </c>
-      <c r="X53" s="22" t="n"/>
-      <c r="Y53" s="22" t="n">
+      <c r="X53" s="18" t="n"/>
+      <c r="Y53" s="18" t="n">
         <v>16662.1</v>
       </c>
-      <c r="Z53" s="22" t="n"/>
-      <c r="AA53" s="22" t="n">
+      <c r="Z53" s="18" t="n"/>
+      <c r="AA53" s="18" t="n">
         <v>41353.6</v>
       </c>
-      <c r="AB53" s="22" t="n"/>
-      <c r="AC53" s="22" t="n">
+      <c r="AB53" s="18" t="n"/>
+      <c r="AC53" s="18" t="n">
         <v>19123.6</v>
       </c>
-      <c r="AD53" s="22" t="n"/>
-      <c r="AE53" s="22" t="n">
+      <c r="AD53" s="18" t="n"/>
+      <c r="AE53" s="18" t="n">
         <v>20410.1</v>
       </c>
-      <c r="AF53" s="22" t="n"/>
-      <c r="AG53" s="22" t="n">
+      <c r="AF53" s="18" t="n"/>
+      <c r="AG53" s="18" t="n">
         <v>220586.2</v>
       </c>
-      <c r="AH53" s="22" t="n">
+      <c r="AH53" s="18" t="n">
         <v>80983.17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A2:AH2"/>
+    <mergeCell ref="A1:AH1"/>
     <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A2:Z2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Presupuesto_Tecnologia_Bolivar_2026.xlsx
+++ b/Presupuesto_Tecnologia_Bolivar_2026.xlsx
@@ -62,7 +62,7 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="000D5C3A"/>
+      <color rgb="000D7A5F"/>
       <sz val="9"/>
     </font>
     <font>
@@ -133,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -159,6 +159,9 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -173,6 +176,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -554,19 +560,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH53"/>
+  <dimension ref="A1:AJ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -589,8 +595,10 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
     <col width="12" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -603,7 +611,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Hoja Tecnologia · Ene–May 2026 · Intelisis ERP + Presupuesto</t>
+          <t>Hoja Tecnologia · Ene–Dic 2026 · Intelisis ERP + Presupuesto</t>
         </is>
       </c>
     </row>
@@ -641,140 +649,150 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>Nombre CC</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>Comentario</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Nombre de proveedor</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Ene Ppto</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Ene Real</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Feb Ppto</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Feb Real</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Mar Ppto</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>Mar Real</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Abr Ppto</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>Abr Real</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>May Ppto</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>May Real</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
         <is>
           <t>Jun Ppto</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>Jun Real</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>Jul Ppto</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
+      <c r="X4" s="5" t="inlineStr">
         <is>
           <t>Jul Real</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>Ago Ppto</t>
         </is>
       </c>
-      <c r="X4" s="5" t="inlineStr">
+      <c r="Z4" s="5" t="inlineStr">
         <is>
           <t>Ago Real</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>Sep Ppto</t>
         </is>
       </c>
-      <c r="Z4" s="5" t="inlineStr">
+      <c r="AB4" s="5" t="inlineStr">
         <is>
           <t>Sep Real</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>Oct Ppto</t>
         </is>
       </c>
-      <c r="AB4" s="5" t="inlineStr">
+      <c r="AD4" s="5" t="inlineStr">
         <is>
           <t>Oct Real</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>Nov Ppto</t>
         </is>
       </c>
-      <c r="AD4" s="5" t="inlineStr">
+      <c r="AF4" s="5" t="inlineStr">
         <is>
           <t>Nov Real</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>Dic Ppto</t>
         </is>
       </c>
-      <c r="AF4" s="5" t="inlineStr">
+      <c r="AH4" s="5" t="inlineStr">
         <is>
           <t>Dic Real</t>
         </is>
       </c>
-      <c r="AG4" s="6" t="inlineStr">
+      <c r="AI4" s="6" t="inlineStr">
         <is>
           <t>Total Ppto</t>
         </is>
       </c>
-      <c r="AH4" s="6" t="inlineStr">
+      <c r="AJ4" s="6" t="inlineStr">
         <is>
           <t>Total Real</t>
         </is>
@@ -786,8 +804,10 @@
           <t>UDESA-SUSCRIPCIONES DE SOFTWARE</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>50</v>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
@@ -799,7 +819,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Suscripciones y publicaciones</t>
         </is>
@@ -811,180 +831,202 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
           <t>Autodesk</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>Grupo Octo/ Cleverbridge gmbh</t>
         </is>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="K5" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="L5" s="11" t="n">
         <v>15707</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="M5" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="L5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="9" t="n">
+      <c r="N5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="N5" s="10" t="n"/>
-      <c r="O5" s="9" t="n">
+      <c r="P5" s="11" t="n"/>
+      <c r="Q5" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="P5" s="10" t="n"/>
-      <c r="Q5" s="9" t="n">
+      <c r="R5" s="11" t="n"/>
+      <c r="S5" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="T5" s="11" t="n">
         <v>1984.94</v>
       </c>
-      <c r="S5" s="9" t="n">
+      <c r="U5" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="T5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="9" t="n">
+      <c r="V5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="V5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="9" t="n">
+      <c r="X5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="X5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="9" t="n">
+      <c r="Z5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="Z5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="9" t="n">
+      <c r="AB5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="AB5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="9" t="n">
+      <c r="AD5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="AD5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="9" t="n">
+      <c r="AF5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="AF5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="11" t="n">
+      <c r="AH5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="12" t="n">
         <v>36000</v>
       </c>
-      <c r="AH5" s="11" t="n">
+      <c r="AJ5" s="12" t="n">
         <v>17691.94</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>UDESA-SUSCRIPCIONES DE SOFTWARE</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Suscripciones y publicaciones</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>412010905</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>Kaspersky IB</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>Grupo Octo</t>
         </is>
       </c>
-      <c r="I6" s="14" t="n"/>
-      <c r="J6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="14" t="n"/>
-      <c r="L6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="14" t="n"/>
-      <c r="N6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="14" t="n"/>
-      <c r="P6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="14" t="n"/>
-      <c r="R6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="14" t="n"/>
-      <c r="T6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="14" t="n"/>
-      <c r="V6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="14" t="n"/>
-      <c r="X6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="14" t="n"/>
-      <c r="Z6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="14" t="n"/>
-      <c r="AB6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="14" t="n">
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="16" t="n"/>
+      <c r="P6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="16" t="n"/>
+      <c r="R6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="16" t="n"/>
+      <c r="T6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="16" t="n"/>
+      <c r="V6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="16" t="n"/>
+      <c r="X6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="16" t="n"/>
+      <c r="Z6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="16" t="n"/>
+      <c r="AB6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="16" t="n"/>
+      <c r="AD6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="AD6" s="15" t="n"/>
-      <c r="AE6" s="14" t="n"/>
-      <c r="AF6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="16" t="n">
+      <c r="AF6" s="17" t="n"/>
+      <c r="AG6" s="16" t="n"/>
+      <c r="AH6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="18" t="n">
         <v>500</v>
       </c>
-      <c r="AH6" s="16" t="n">
+      <c r="AJ6" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -994,8 +1036,10 @@
           <t>UDESA-SUSCRIPCIONES DE SOFTWARE</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>280</v>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
@@ -1007,7 +1051,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Suscripciones y publicaciones</t>
         </is>
@@ -1019,148 +1063,170 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
           <t>Microsoft 365 IB</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>DATA &amp; GRAPHICS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="10" t="n"/>
-      <c r="K7" s="9" t="n"/>
-      <c r="L7" s="10" t="n">
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="11" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="11" t="n">
         <v>378.77</v>
       </c>
-      <c r="M7" s="9" t="n"/>
-      <c r="N7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="9" t="n"/>
-      <c r="P7" s="10" t="n">
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="11" t="n">
         <v>1385.88</v>
       </c>
-      <c r="Q7" s="9" t="n"/>
-      <c r="R7" s="10" t="n">
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="11" t="n">
         <v>410.22</v>
       </c>
-      <c r="S7" s="9" t="n"/>
-      <c r="T7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="9" t="n"/>
-      <c r="V7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="9" t="n"/>
-      <c r="X7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="9" t="n"/>
-      <c r="Z7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="9" t="n">
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="10" t="n"/>
+      <c r="X7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="10" t="n"/>
+      <c r="Z7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="10" t="n"/>
+      <c r="AB7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="10" t="n">
         <v>25600</v>
       </c>
-      <c r="AB7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="9" t="n"/>
-      <c r="AD7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="9" t="n"/>
-      <c r="AF7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="11" t="n">
+      <c r="AD7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="10" t="n"/>
+      <c r="AF7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="10" t="n"/>
+      <c r="AH7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="12" t="n">
         <v>25600</v>
       </c>
-      <c r="AH7" s="11" t="n">
+      <c r="AJ7" s="12" t="n">
         <v>2174.87</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>ADM-LICENCIAS DE PROGRAMAS</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>Licencias de programas</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>412010904</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>Licencia Fortigate</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="J8" s="15" t="inlineStr">
         <is>
           <t>LIBERTY NETWORKS EL SALVADOR / JM TELCOM</t>
         </is>
       </c>
-      <c r="I8" s="14" t="n"/>
-      <c r="J8" s="15" t="n"/>
-      <c r="K8" s="14" t="n"/>
-      <c r="L8" s="15" t="n"/>
-      <c r="M8" s="14" t="n"/>
-      <c r="N8" s="15" t="n"/>
-      <c r="O8" s="14" t="n"/>
-      <c r="P8" s="15" t="n">
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="16" t="n"/>
+      <c r="N8" s="17" t="n"/>
+      <c r="O8" s="16" t="n"/>
+      <c r="P8" s="17" t="n"/>
+      <c r="Q8" s="16" t="n"/>
+      <c r="R8" s="17" t="n">
         <v>1895</v>
       </c>
-      <c r="Q8" s="14" t="n"/>
-      <c r="R8" s="15" t="n"/>
-      <c r="S8" s="14" t="n"/>
-      <c r="T8" s="15" t="n"/>
-      <c r="U8" s="14" t="n"/>
-      <c r="V8" s="15" t="n"/>
-      <c r="W8" s="14" t="n"/>
-      <c r="X8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="14" t="n"/>
-      <c r="Z8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="14" t="n"/>
-      <c r="AB8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="14" t="n"/>
-      <c r="AD8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="14" t="n"/>
-      <c r="AF8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="16" t="n">
+      <c r="S8" s="16" t="n"/>
+      <c r="T8" s="17" t="n"/>
+      <c r="U8" s="16" t="n"/>
+      <c r="V8" s="17" t="n"/>
+      <c r="W8" s="16" t="n"/>
+      <c r="X8" s="17" t="n"/>
+      <c r="Y8" s="16" t="n"/>
+      <c r="Z8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="16" t="n"/>
+      <c r="AB8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="16" t="n"/>
+      <c r="AD8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="16" t="n"/>
+      <c r="AF8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="16" t="n"/>
+      <c r="AH8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="18" t="n">
         <v>1895</v>
       </c>
     </row>
@@ -1170,8 +1236,10 @@
           <t>ADM-COMUNICACIONES</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>280</v>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
@@ -1183,7 +1251,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Comunicaciones</t>
         </is>
@@ -1195,208 +1263,230 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
           <t>Internet IB</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>LIBERTY NETWORKS EL SALVADOR, S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="K9" s="10" t="n">
         <v>600</v>
       </c>
-      <c r="J9" s="10" t="n">
+      <c r="L9" s="11" t="n">
         <v>600</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="M9" s="10" t="n">
         <v>600</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="N9" s="11" t="n">
         <v>600</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="O9" s="10" t="n">
         <v>600</v>
       </c>
-      <c r="N9" s="10" t="n">
+      <c r="P9" s="11" t="n">
         <v>600</v>
       </c>
-      <c r="O9" s="9" t="n">
+      <c r="Q9" s="10" t="n">
         <v>600</v>
       </c>
-      <c r="P9" s="10" t="n">
+      <c r="R9" s="11" t="n">
         <v>600</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="S9" s="10" t="n">
         <v>600</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="T9" s="11" t="n">
         <v>600</v>
       </c>
-      <c r="S9" s="9" t="n">
+      <c r="U9" s="10" t="n">
         <v>600</v>
       </c>
-      <c r="T9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="9" t="n">
+      <c r="V9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="10" t="n">
         <v>600</v>
       </c>
-      <c r="V9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="9" t="n">
+      <c r="X9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="10" t="n">
         <v>600</v>
       </c>
-      <c r="X9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="9" t="n">
+      <c r="Z9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="10" t="n">
         <v>600</v>
       </c>
-      <c r="Z9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="9" t="n">
+      <c r="AB9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="10" t="n">
         <v>600</v>
       </c>
-      <c r="AB9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="9" t="n">
+      <c r="AD9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="10" t="n">
         <v>600</v>
       </c>
-      <c r="AD9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="9" t="n">
+      <c r="AF9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="10" t="n">
         <v>600</v>
       </c>
-      <c r="AF9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="11" t="n">
+      <c r="AH9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="12" t="n">
         <v>7200</v>
       </c>
-      <c r="AH9" s="11" t="n">
+      <c r="AJ9" s="12" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>ADM-LICENCIAS DE PROGRAMAS</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Licencias de programas</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>412010904</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
         <is>
           <t>Intelisis</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="J10" s="15" t="inlineStr">
         <is>
           <t>Grupo Octo</t>
         </is>
       </c>
-      <c r="I10" s="14" t="n">
+      <c r="K10" s="16" t="n">
         <v>4200</v>
       </c>
-      <c r="J10" s="15" t="n">
+      <c r="L10" s="17" t="n">
         <v>3500</v>
       </c>
-      <c r="K10" s="14" t="n">
+      <c r="M10" s="16" t="n">
         <v>4200</v>
       </c>
-      <c r="L10" s="15" t="n">
+      <c r="N10" s="17" t="n">
         <v>3500</v>
       </c>
-      <c r="M10" s="14" t="n">
+      <c r="O10" s="16" t="n">
         <v>4200</v>
       </c>
-      <c r="N10" s="15" t="n">
+      <c r="P10" s="17" t="n">
         <v>3500</v>
       </c>
-      <c r="O10" s="14" t="n">
+      <c r="Q10" s="16" t="n">
         <v>4200</v>
       </c>
-      <c r="P10" s="15" t="n">
+      <c r="R10" s="17" t="n">
         <v>3500</v>
       </c>
-      <c r="Q10" s="14" t="n">
+      <c r="S10" s="16" t="n">
         <v>4200</v>
       </c>
-      <c r="R10" s="15" t="n">
+      <c r="T10" s="17" t="n">
         <v>3500</v>
       </c>
-      <c r="S10" s="14" t="n">
+      <c r="U10" s="16" t="n">
         <v>4200</v>
       </c>
-      <c r="T10" s="15" t="n">
+      <c r="V10" s="17" t="n">
         <v>3500</v>
       </c>
-      <c r="U10" s="14" t="n">
+      <c r="W10" s="16" t="n">
         <v>4200</v>
       </c>
-      <c r="V10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="14" t="n">
+      <c r="X10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="16" t="n">
         <v>4200</v>
       </c>
-      <c r="X10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="14" t="n">
+      <c r="Z10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="16" t="n">
         <v>4200</v>
       </c>
-      <c r="Z10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="14" t="n">
+      <c r="AB10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="16" t="n">
         <v>4200</v>
       </c>
-      <c r="AB10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="14" t="n">
+      <c r="AD10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="16" t="n">
         <v>4200</v>
       </c>
-      <c r="AD10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="14" t="n">
+      <c r="AF10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="16" t="n">
         <v>4200</v>
       </c>
-      <c r="AF10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="16" t="n">
+      <c r="AH10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="18" t="n">
         <v>50400</v>
       </c>
-      <c r="AH10" s="16" t="n">
+      <c r="AJ10" s="18" t="n">
         <v>21000</v>
       </c>
     </row>
@@ -1406,8 +1496,10 @@
           <t>UDESA-SERVICIOS DE TECNOLOGÍA</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>280</v>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
@@ -1419,7 +1511,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Servicios Generales de Técnologia</t>
         </is>
@@ -1431,200 +1523,222 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
           <t>Desarrollo Intelisis</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>Grupo Octo</t>
         </is>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="K11" s="10" t="n">
         <v>583</v>
       </c>
-      <c r="J11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="9" t="n">
+      <c r="L11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="10" t="n">
         <v>583</v>
       </c>
-      <c r="L11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="9" t="n">
+      <c r="N11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="10" t="n">
         <v>583</v>
       </c>
-      <c r="N11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="9" t="n">
+      <c r="P11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="10" t="n">
         <v>583</v>
       </c>
-      <c r="P11" s="10" t="n"/>
-      <c r="Q11" s="9" t="n">
+      <c r="R11" s="11" t="n"/>
+      <c r="S11" s="10" t="n">
         <v>583</v>
       </c>
-      <c r="R11" s="10" t="n"/>
-      <c r="S11" s="9" t="n">
+      <c r="T11" s="11" t="n"/>
+      <c r="U11" s="10" t="n">
         <v>583</v>
       </c>
-      <c r="T11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="9" t="n">
+      <c r="V11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="10" t="n">
         <v>583</v>
       </c>
-      <c r="V11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="9" t="n">
+      <c r="X11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="10" t="n">
         <v>583</v>
       </c>
-      <c r="X11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="9" t="n">
+      <c r="Z11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="10" t="n">
         <v>583</v>
       </c>
-      <c r="Z11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="9" t="n">
+      <c r="AB11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="10" t="n">
         <v>583</v>
       </c>
-      <c r="AB11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="9" t="n">
+      <c r="AD11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="10" t="n">
         <v>583</v>
       </c>
-      <c r="AD11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="9" t="n">
+      <c r="AF11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="10" t="n">
         <v>583</v>
       </c>
-      <c r="AF11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="11" t="n">
+      <c r="AH11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="12" t="n">
         <v>6996</v>
       </c>
-      <c r="AH11" s="11" t="n">
+      <c r="AJ11" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>UDESA-SUSCRIPCIONES DE SOFTWARE</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Suscripciones y publicaciones</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>412010905</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t>Azure</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t>DATA &amp; GRAPHICS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I12" s="14" t="n">
+      <c r="K12" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="J12" s="15" t="n">
+      <c r="L12" s="17" t="n">
         <v>895.84</v>
       </c>
-      <c r="K12" s="14" t="n">
+      <c r="M12" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="L12" s="15" t="n"/>
-      <c r="M12" s="14" t="n">
+      <c r="N12" s="17" t="n"/>
+      <c r="O12" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="N12" s="15" t="n"/>
-      <c r="O12" s="14" t="n">
+      <c r="P12" s="17" t="n"/>
+      <c r="Q12" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="P12" s="15" t="n">
+      <c r="R12" s="17" t="n">
         <v>1919.35</v>
       </c>
-      <c r="Q12" s="14" t="n">
+      <c r="S12" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="R12" s="15" t="n">
+      <c r="T12" s="17" t="n">
         <v>1890.51</v>
       </c>
-      <c r="S12" s="14" t="n">
+      <c r="U12" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="T12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="14" t="n">
+      <c r="V12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="V12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="14" t="n">
+      <c r="X12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="X12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="14" t="n">
+      <c r="Z12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="Z12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="14" t="n">
+      <c r="AB12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="AB12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="14" t="n">
+      <c r="AD12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="AD12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="14" t="n">
+      <c r="AF12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="AF12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="16" t="n">
+      <c r="AH12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="18" t="n">
         <v>8400</v>
       </c>
-      <c r="AH12" s="16" t="n">
+      <c r="AJ12" s="18" t="n">
         <v>4705.7</v>
       </c>
     </row>
@@ -1634,8 +1748,10 @@
           <t>ADM-LICENCIAS DE PROGRAMAS</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
-        <v>280</v>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
@@ -1647,7 +1763,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Licencias de programas</t>
         </is>
@@ -1659,170 +1775,192 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
           <t>Licencias FortiAP</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>LIBERTY NETWORKS EL SALVADOR, S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="9" t="n"/>
-      <c r="L13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9" t="n"/>
-      <c r="N13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="9" t="n"/>
-      <c r="P13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="9" t="n"/>
-      <c r="R13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="9" t="n"/>
-      <c r="T13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="9" t="n">
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="10" t="n"/>
+      <c r="V13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="V13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="9" t="n"/>
-      <c r="X13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="9" t="n"/>
-      <c r="Z13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="9" t="n"/>
-      <c r="AB13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="9" t="n"/>
-      <c r="AD13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="9" t="n"/>
-      <c r="AF13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="11" t="n">
+      <c r="X13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="10" t="n"/>
+      <c r="Z13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="10" t="n"/>
+      <c r="AB13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="10" t="n"/>
+      <c r="AD13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="10" t="n"/>
+      <c r="AF13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="10" t="n"/>
+      <c r="AH13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="AH13" s="11" t="n">
+      <c r="AJ13" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>ADM-MANTENIMIENTO DE MOBILIARIO Y EQUIPO DE OFINA</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>Mantenimiento de mobiliario y equipo de ofina</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>412010602</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t>Mantenimiento informatico</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t>CRUZ TERMINIO, LUIS DANIEL</t>
         </is>
       </c>
-      <c r="I14" s="14" t="n"/>
-      <c r="J14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="14" t="n"/>
-      <c r="L14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="14" t="n">
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="16" t="n">
         <v>1900</v>
       </c>
-      <c r="N14" s="15" t="n">
+      <c r="P14" s="17" t="n">
         <v>1889</v>
       </c>
-      <c r="O14" s="14" t="n"/>
-      <c r="P14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14" t="n"/>
-      <c r="R14" s="15" t="n">
+      <c r="Q14" s="16" t="n"/>
+      <c r="R14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="16" t="n"/>
+      <c r="T14" s="17" t="n">
         <v>1969</v>
       </c>
-      <c r="S14" s="14" t="n">
+      <c r="U14" s="16" t="n">
         <v>1900</v>
       </c>
-      <c r="T14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="14" t="n"/>
-      <c r="V14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="14" t="n"/>
-      <c r="X14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="14" t="n">
+      <c r="V14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="16" t="n"/>
+      <c r="X14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="16" t="n"/>
+      <c r="Z14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="16" t="n">
         <v>1900</v>
       </c>
-      <c r="Z14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="14" t="n"/>
-      <c r="AB14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="14" t="n"/>
-      <c r="AD14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="14" t="n">
+      <c r="AB14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="16" t="n"/>
+      <c r="AD14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="16" t="n"/>
+      <c r="AF14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="16" t="n">
         <v>1900</v>
       </c>
-      <c r="AF14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="16" t="n">
+      <c r="AH14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="18" t="n">
         <v>7600</v>
       </c>
-      <c r="AH14" s="16" t="n">
+      <c r="AJ14" s="18" t="n">
         <v>3858</v>
       </c>
     </row>
@@ -1832,8 +1970,10 @@
           <t>UDESA-SOPORTE TÉCNICO TERCERIZADO</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
-        <v>280</v>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
@@ -1845,7 +1985,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Servicios Generales de Técnologia</t>
         </is>
@@ -1857,206 +1997,228 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
           <t>Tecnico destacado KNK</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>CANIZALEZ HERNANDEZ LUDWIN IVAN</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="K15" s="10" t="n">
         <v>800</v>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="L15" s="11" t="n">
         <v>1100</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="M15" s="10" t="n">
         <v>800</v>
       </c>
-      <c r="L15" s="10" t="n">
+      <c r="N15" s="11" t="n">
         <v>1210</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="O15" s="10" t="n">
         <v>800</v>
       </c>
-      <c r="N15" s="10" t="n">
+      <c r="P15" s="11" t="n">
         <v>1100</v>
       </c>
-      <c r="O15" s="9" t="n">
+      <c r="Q15" s="10" t="n">
         <v>800</v>
       </c>
-      <c r="P15" s="10" t="n">
+      <c r="R15" s="11" t="n">
         <v>1100</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="S15" s="10" t="n">
         <v>800</v>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="T15" s="11" t="n">
         <v>1100</v>
       </c>
-      <c r="S15" s="9" t="n">
+      <c r="U15" s="10" t="n">
         <v>800</v>
       </c>
-      <c r="T15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="9" t="n">
+      <c r="V15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="10" t="n">
         <v>800</v>
       </c>
-      <c r="V15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="9" t="n">
+      <c r="X15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="10" t="n">
         <v>800</v>
       </c>
-      <c r="X15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="9" t="n">
+      <c r="Z15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="10" t="n">
         <v>800</v>
       </c>
-      <c r="Z15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="9" t="n">
+      <c r="AB15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="10" t="n">
         <v>800</v>
       </c>
-      <c r="AB15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="9" t="n">
+      <c r="AD15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="10" t="n">
         <v>800</v>
       </c>
-      <c r="AD15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="9" t="n">
+      <c r="AF15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="10" t="n">
         <v>800</v>
       </c>
-      <c r="AF15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="11" t="n">
+      <c r="AH15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="12" t="n">
         <v>9600</v>
       </c>
-      <c r="AH15" s="11" t="n">
+      <c r="AJ15" s="12" t="n">
         <v>5610</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>UDESA-SOPORTE TÉCNICO TERCERIZADO</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>Servicios Generales de Técnologia</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>412011220</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>Soporte visitas de campo</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="J16" s="15" t="inlineStr">
         <is>
           <t>CANIZALEZ HERNANDEZ LUDWIN IVAN</t>
         </is>
       </c>
-      <c r="I16" s="14" t="n">
+      <c r="K16" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="J16" s="15" t="n"/>
-      <c r="K16" s="14" t="n">
+      <c r="L16" s="17" t="n"/>
+      <c r="M16" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="L16" s="15" t="n">
+      <c r="N16" s="17" t="n">
         <v>207.9</v>
       </c>
-      <c r="M16" s="14" t="n">
+      <c r="O16" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="N16" s="15" t="n">
+      <c r="P16" s="17" t="n">
         <v>600.6</v>
       </c>
-      <c r="O16" s="14" t="n">
+      <c r="Q16" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="P16" s="15" t="n">
+      <c r="R16" s="17" t="n">
         <v>300.3</v>
       </c>
-      <c r="Q16" s="14" t="n">
+      <c r="S16" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="R16" s="15" t="n">
+      <c r="T16" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="S16" s="14" t="n">
+      <c r="U16" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="T16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="14" t="n">
+      <c r="V16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="V16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="14" t="n">
+      <c r="X16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="X16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="14" t="n">
+      <c r="Z16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="Z16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="14" t="n">
+      <c r="AB16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="AB16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="14" t="n">
+      <c r="AD16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="AD16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="14" t="n">
+      <c r="AF16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="AF16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="16" t="n">
+      <c r="AH16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="18" t="n">
         <v>3600</v>
       </c>
-      <c r="AH16" s="16" t="n">
+      <c r="AJ16" s="18" t="n">
         <v>1208.8</v>
       </c>
     </row>
@@ -2066,8 +2228,10 @@
           <t>ADM-MANTENIMIENTO DE MOBILIARIO Y EQUIPO DE OFINA</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
-        <v>280</v>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
@@ -2079,7 +2243,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Mantenimiento de mobiliario y equipo de ofina</t>
         </is>
@@ -2091,174 +2255,196 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
           <t>Mantenimiento racks IB</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>CRUZ TERMINIO, LUIS DANIEL</t>
         </is>
       </c>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="9" t="n"/>
-      <c r="L17" s="10" t="n"/>
-      <c r="M17" s="9" t="n">
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="10" t="n"/>
+      <c r="N17" s="11" t="n"/>
+      <c r="O17" s="10" t="n">
         <v>140</v>
       </c>
-      <c r="N17" s="10" t="n">
+      <c r="P17" s="11" t="n">
         <v>140</v>
       </c>
-      <c r="O17" s="9" t="n"/>
-      <c r="P17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="9" t="n"/>
-      <c r="R17" s="10" t="n">
+      <c r="Q17" s="10" t="n"/>
+      <c r="R17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="10" t="n"/>
+      <c r="T17" s="11" t="n">
         <v>185</v>
       </c>
-      <c r="S17" s="9" t="n">
+      <c r="U17" s="10" t="n">
         <v>140</v>
       </c>
-      <c r="T17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="9" t="n"/>
-      <c r="V17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="9" t="n"/>
-      <c r="X17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="9" t="n">
+      <c r="V17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="10" t="n"/>
+      <c r="X17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="10" t="n"/>
+      <c r="Z17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="10" t="n">
         <v>140</v>
       </c>
-      <c r="Z17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="9" t="n"/>
-      <c r="AB17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="9" t="n"/>
-      <c r="AD17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="9" t="n">
+      <c r="AB17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="10" t="n"/>
+      <c r="AD17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="10" t="n"/>
+      <c r="AF17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="10" t="n">
         <v>140</v>
       </c>
-      <c r="AF17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="11" t="n">
+      <c r="AH17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="12" t="n">
         <v>560</v>
       </c>
-      <c r="AH17" s="11" t="n">
+      <c r="AJ17" s="12" t="n">
         <v>325</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>ADM-MANTENIMIENTO DE MOBILIARIO Y EQUIPO DE OFINA</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>Mantenimiento de mobiliario y equipo de ofina</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>412010602</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>Mantenimiento UPS IB</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="J18" s="15" t="inlineStr">
         <is>
           <t>CRUZ TERMINIO, LUIS DANIEL</t>
         </is>
       </c>
-      <c r="I18" s="14" t="n"/>
-      <c r="J18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="14" t="n"/>
-      <c r="L18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="14" t="n">
+      <c r="K18" s="16" t="n"/>
+      <c r="L18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="16" t="n"/>
+      <c r="N18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="N18" s="15" t="n">
+      <c r="P18" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="O18" s="14" t="n"/>
-      <c r="P18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="14" t="n"/>
-      <c r="R18" s="15" t="n">
+      <c r="Q18" s="16" t="n"/>
+      <c r="R18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="16" t="n"/>
+      <c r="T18" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="S18" s="14" t="n">
+      <c r="U18" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="T18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="14" t="n"/>
-      <c r="V18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="14" t="n"/>
-      <c r="X18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="14" t="n">
+      <c r="V18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="16" t="n"/>
+      <c r="X18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="16" t="n"/>
+      <c r="Z18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="Z18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="14" t="n"/>
-      <c r="AB18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="14" t="n"/>
-      <c r="AD18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="14" t="n">
+      <c r="AB18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="16" t="n"/>
+      <c r="AD18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="16" t="n"/>
+      <c r="AF18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="AF18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="16" t="n">
+      <c r="AH18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="18" t="n">
         <v>500</v>
       </c>
-      <c r="AH18" s="16" t="n">
+      <c r="AJ18" s="18" t="n">
         <v>200</v>
       </c>
     </row>
@@ -2268,8 +2454,10 @@
           <t>ADM-ACCESORIOS, PAQUETES Y PROGRAMAS</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
-        <v>280</v>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
@@ -2281,7 +2469,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
@@ -2293,186 +2481,208 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
           <t>Baterias UPS</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>CRUZ TERMINIO, LUIS DANIEL</t>
         </is>
       </c>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="9" t="n"/>
-      <c r="L19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="9" t="n"/>
-      <c r="N19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="9" t="n"/>
-      <c r="P19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="9" t="n"/>
-      <c r="R19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="9" t="n"/>
-      <c r="T19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="9" t="n"/>
-      <c r="V19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" s="9" t="n"/>
-      <c r="X19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="9" t="n"/>
-      <c r="Z19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="9" t="n"/>
-      <c r="AB19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="9" t="n"/>
-      <c r="AD19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" s="9" t="n">
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="10" t="n"/>
+      <c r="P19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="10" t="n"/>
+      <c r="R19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="10" t="n"/>
+      <c r="V19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="10" t="n"/>
+      <c r="X19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="10" t="n"/>
+      <c r="Z19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="10" t="n"/>
+      <c r="AB19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="10" t="n"/>
+      <c r="AD19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="10" t="n"/>
+      <c r="AF19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="10" t="n">
         <v>750</v>
       </c>
-      <c r="AF19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="11" t="n">
+      <c r="AH19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="AH19" s="11" t="n">
+      <c r="AJ19" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>ADM-MANTENIMIENTO DE MOBILIARIO Y EQUIPO DE OFINA</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>Mantenimiento de mobiliario y equipo de ofina</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>412010602</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>Mantenimiento impresores RICOH</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="J20" s="15" t="inlineStr">
         <is>
           <t>RICOH EL SALVADOR, S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I20" s="14" t="n">
+      <c r="K20" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="J20" s="15" t="n">
+      <c r="L20" s="17" t="n">
         <v>72</v>
       </c>
-      <c r="K20" s="14" t="n">
+      <c r="M20" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="L20" s="15" t="n">
+      <c r="N20" s="17" t="n">
         <v>216</v>
       </c>
-      <c r="M20" s="14" t="n">
+      <c r="O20" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="N20" s="15" t="n">
+      <c r="P20" s="17" t="n">
         <v>354.56</v>
       </c>
-      <c r="O20" s="14" t="n">
+      <c r="Q20" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="P20" s="15" t="n">
+      <c r="R20" s="17" t="n">
         <v>394.25</v>
       </c>
-      <c r="Q20" s="14" t="n">
+      <c r="S20" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="R20" s="15" t="n">
+      <c r="T20" s="17" t="n">
         <v>322.25</v>
       </c>
-      <c r="S20" s="14" t="n">
+      <c r="U20" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="T20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="14" t="n">
+      <c r="V20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="V20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="14" t="n">
+      <c r="X20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="X20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="14" t="n">
+      <c r="Z20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="Z20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="14" t="n">
+      <c r="AB20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="AB20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="14" t="n">
+      <c r="AD20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="AD20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="14" t="n">
+      <c r="AF20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="AF20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="16" t="n">
+      <c r="AH20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="18" t="n">
         <v>1800</v>
       </c>
-      <c r="AH20" s="16" t="n">
+      <c r="AJ20" s="18" t="n">
         <v>1359.06</v>
       </c>
     </row>
@@ -2482,8 +2692,10 @@
           <t>ADM-CONSUMIBLES FOTOCOPIADORA</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
-        <v>280</v>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
@@ -2495,7 +2707,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Consumibles y accesorios equipos de oficina</t>
         </is>
@@ -2507,178 +2719,200 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
           <t>Impresiones adicionales color</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>RICOH EL SALVADOR, S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="K21" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="J21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="9" t="n"/>
-      <c r="L21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="9" t="n"/>
-      <c r="N21" s="10" t="n"/>
-      <c r="O21" s="9" t="n">
+      <c r="L21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="10" t="n"/>
+      <c r="N21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10" t="n"/>
+      <c r="P21" s="11" t="n"/>
+      <c r="Q21" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="P21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="9" t="n"/>
-      <c r="R21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="9" t="n"/>
-      <c r="T21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="9" t="n">
+      <c r="R21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="10" t="n"/>
+      <c r="T21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="10" t="n"/>
+      <c r="V21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="V21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="9" t="n"/>
-      <c r="X21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="9" t="n"/>
-      <c r="Z21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="9" t="n">
+      <c r="X21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="10" t="n"/>
+      <c r="Z21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="10" t="n"/>
+      <c r="AB21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="AB21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="9" t="n"/>
-      <c r="AD21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="9" t="n"/>
-      <c r="AF21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="11" t="n">
+      <c r="AD21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="10" t="n"/>
+      <c r="AF21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="10" t="n"/>
+      <c r="AH21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="12" t="n">
         <v>1600</v>
       </c>
-      <c r="AH21" s="11" t="n">
+      <c r="AJ21" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>ADM-CONSUMIBLES FOTOCOPIADORA</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>Consumibles y accesorios equipos de oficina</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>412010906</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
         <is>
           <t>Toner impresores</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="J22" s="15" t="inlineStr">
         <is>
           <t>RICOH EL SALVADOR, S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I22" s="14" t="n">
+      <c r="K22" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="J22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="14" t="n"/>
-      <c r="L22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="14" t="n">
+      <c r="L22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="16" t="n"/>
+      <c r="N22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="N22" s="15" t="n">
+      <c r="P22" s="17" t="n">
         <v>522</v>
       </c>
-      <c r="O22" s="14" t="n"/>
-      <c r="P22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="14" t="n">
+      <c r="Q22" s="16" t="n"/>
+      <c r="R22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="R22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="14" t="n"/>
-      <c r="T22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="14" t="n">
+      <c r="T22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="16" t="n"/>
+      <c r="V22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="V22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="14" t="n"/>
-      <c r="X22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="14" t="n">
+      <c r="X22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="16" t="n"/>
+      <c r="Z22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="Z22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="14" t="n"/>
-      <c r="AB22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="14" t="n">
+      <c r="AB22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="16" t="n"/>
+      <c r="AD22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="AD22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="14" t="n"/>
-      <c r="AF22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="16" t="n">
+      <c r="AF22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="16" t="n"/>
+      <c r="AH22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="18" t="n">
         <v>3300</v>
       </c>
-      <c r="AH22" s="16" t="n">
+      <c r="AJ22" s="18" t="n">
         <v>522</v>
       </c>
     </row>
@@ -2688,8 +2922,10 @@
           <t>ADM-MANTENIMIENTO DE PLANTA TELEFÓNICA</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
-        <v>280</v>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
@@ -2701,7 +2937,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Mantenimiento de planta telefónica</t>
         </is>
@@ -2713,192 +2949,214 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
           <t>Mantenimiento planta telefonica</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>EBD CENTROAMERICA S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="K23" s="10" t="n">
         <v>380</v>
       </c>
-      <c r="J23" s="10" t="n">
+      <c r="L23" s="11" t="n">
         <v>335.16</v>
       </c>
-      <c r="K23" s="9" t="n"/>
-      <c r="L23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="9" t="n"/>
-      <c r="N23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="9" t="n">
+      <c r="M23" s="10" t="n"/>
+      <c r="N23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10" t="n"/>
+      <c r="P23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="10" t="n">
         <v>380</v>
       </c>
-      <c r="P23" s="10" t="n">
+      <c r="R23" s="11" t="n">
         <v>335.16</v>
       </c>
-      <c r="Q23" s="9" t="n"/>
-      <c r="R23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="9" t="n"/>
-      <c r="T23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" s="9" t="n">
+      <c r="S23" s="10" t="n"/>
+      <c r="T23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="10" t="n"/>
+      <c r="V23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="10" t="n">
         <v>380</v>
       </c>
-      <c r="V23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" s="9" t="n"/>
-      <c r="X23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="9" t="n"/>
-      <c r="Z23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="9" t="n">
+      <c r="X23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="10" t="n"/>
+      <c r="Z23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="10" t="n"/>
+      <c r="AB23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="10" t="n">
         <v>380</v>
       </c>
-      <c r="AB23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="9" t="n"/>
-      <c r="AD23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="9" t="n"/>
-      <c r="AF23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="11" t="n">
+      <c r="AD23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="10" t="n"/>
+      <c r="AF23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="10" t="n"/>
+      <c r="AH23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="12" t="n">
         <v>1520</v>
       </c>
-      <c r="AH23" s="11" t="n">
+      <c r="AJ23" s="12" t="n">
         <v>670.3200000000001</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>ADM-LICENCIAS DE PROGRAMAS</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Finanzas</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>Licencias de programas</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>412010904</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
         <is>
           <t>Laserfiche</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="J24" s="15" t="inlineStr">
         <is>
           <t>RICOH EL SALVADOR, S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I24" s="14" t="n">
+      <c r="K24" s="16" t="n">
         <v>525.1</v>
       </c>
-      <c r="J24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="14" t="n">
+      <c r="L24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="16" t="n">
         <v>525.1</v>
       </c>
-      <c r="L24" s="15" t="n">
+      <c r="N24" s="17" t="n">
         <v>2480.35</v>
       </c>
-      <c r="M24" s="14" t="n">
+      <c r="O24" s="16" t="n">
         <v>525.1</v>
       </c>
-      <c r="N24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="14" t="n">
+      <c r="P24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="16" t="n">
         <v>525.1</v>
       </c>
-      <c r="P24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="14" t="n">
+      <c r="R24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="16" t="n">
         <v>525.1</v>
       </c>
-      <c r="R24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="14" t="n">
+      <c r="T24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="16" t="n">
         <v>525.1</v>
       </c>
-      <c r="T24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="14" t="n">
+      <c r="V24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="16" t="n">
         <v>525.1</v>
       </c>
-      <c r="V24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="14" t="n">
+      <c r="X24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="16" t="n">
         <v>525.1</v>
       </c>
-      <c r="X24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="14" t="n">
+      <c r="Z24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="16" t="n">
         <v>525.1</v>
       </c>
-      <c r="Z24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="14" t="n">
+      <c r="AB24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="16" t="n">
         <v>525.1</v>
       </c>
-      <c r="AB24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="14" t="n">
+      <c r="AD24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="16" t="n">
         <v>525.1</v>
       </c>
-      <c r="AD24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="14" t="n">
+      <c r="AF24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="16" t="n">
         <v>525.1</v>
       </c>
-      <c r="AF24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="16" t="n">
+      <c r="AH24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="18" t="n">
         <v>6301.200000000002</v>
       </c>
-      <c r="AH24" s="16" t="n">
+      <c r="AJ24" s="18" t="n">
         <v>2480.35</v>
       </c>
     </row>
@@ -2908,8 +3166,10 @@
           <t>ADM-LICENCIAS DE PROGRAMAS</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
-        <v>50</v>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
@@ -2921,7 +3181,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>Licencias de programas</t>
         </is>
@@ -2933,182 +3193,204 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
           <t>Sketchup pro</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>Cleverbridge GmbH</t>
         </is>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="K25" s="10" t="n">
         <v>350</v>
       </c>
-      <c r="J25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="9" t="n"/>
-      <c r="L25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="9" t="n">
+      <c r="L25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="10" t="n"/>
+      <c r="N25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="10" t="n">
         <v>350</v>
       </c>
-      <c r="N25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="9" t="n"/>
-      <c r="P25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="9" t="n"/>
-      <c r="R25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="9" t="n"/>
-      <c r="T25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="9" t="n"/>
-      <c r="V25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" s="9" t="n"/>
-      <c r="X25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="9" t="n"/>
-      <c r="Z25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="9" t="n"/>
-      <c r="AB25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="9" t="n"/>
-      <c r="AD25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" s="9" t="n"/>
-      <c r="AF25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" s="11" t="n">
+      <c r="P25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="10" t="n"/>
+      <c r="R25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="10" t="n"/>
+      <c r="T25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="10" t="n"/>
+      <c r="V25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="10" t="n"/>
+      <c r="X25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="10" t="n"/>
+      <c r="Z25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="10" t="n"/>
+      <c r="AB25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="10" t="n"/>
+      <c r="AD25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="10" t="n"/>
+      <c r="AF25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="10" t="n"/>
+      <c r="AH25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="12" t="n">
         <v>700</v>
       </c>
-      <c r="AH25" s="11" t="n">
+      <c r="AJ25" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>UDESA-SUSCRIPCIONES DE SOFTWARE</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>Suscripciones y publicaciones</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>412010905</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
         <is>
           <t>GLPi (Inventario IT)</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="J26" s="15" t="inlineStr">
         <is>
           <t>TECLIB</t>
         </is>
       </c>
-      <c r="I26" s="14" t="n">
+      <c r="K26" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="J26" s="15" t="n"/>
-      <c r="K26" s="14" t="n">
+      <c r="L26" s="17" t="n"/>
+      <c r="M26" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="L26" s="15" t="n">
+      <c r="N26" s="17" t="n">
         <v>112.9</v>
       </c>
-      <c r="M26" s="14" t="n">
+      <c r="O26" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="N26" s="15" t="n"/>
-      <c r="O26" s="14" t="n">
+      <c r="P26" s="17" t="n"/>
+      <c r="Q26" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="P26" s="15" t="n"/>
-      <c r="Q26" s="14" t="n">
+      <c r="R26" s="17" t="n"/>
+      <c r="S26" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="R26" s="15" t="n">
+      <c r="T26" s="17" t="n">
         <v>111.35</v>
       </c>
-      <c r="S26" s="14" t="n">
+      <c r="U26" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="T26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="14" t="n">
+      <c r="V26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="V26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="14" t="n">
+      <c r="X26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="X26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="14" t="n">
+      <c r="Z26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="Z26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="14" t="n">
+      <c r="AB26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="AB26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="14" t="n">
+      <c r="AD26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="AD26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" s="14" t="n">
+      <c r="AF26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="AF26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="16" t="n">
+      <c r="AH26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="18" t="n">
         <v>540</v>
       </c>
-      <c r="AH26" s="16" t="n">
+      <c r="AJ26" s="18" t="n">
         <v>224.25</v>
       </c>
     </row>
@@ -3118,8 +3400,10 @@
           <t>ADM-LICENCIAS DE PROGRAMAS</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n">
-        <v>50</v>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
@@ -3131,7 +3415,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>Licencias de programas</t>
         </is>
@@ -3143,182 +3427,204 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
           <t>Photoshop arquitectas</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>Cleverbridge GmbH</t>
         </is>
       </c>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="9" t="n"/>
-      <c r="L27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="9" t="n">
+      <c r="K27" s="10" t="n"/>
+      <c r="L27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="10" t="n"/>
+      <c r="N27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="N27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="9" t="n"/>
-      <c r="P27" s="10" t="n"/>
-      <c r="Q27" s="9" t="n"/>
-      <c r="R27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="9" t="n"/>
-      <c r="T27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="9" t="n"/>
-      <c r="V27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" s="9" t="n"/>
-      <c r="X27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="9" t="n"/>
-      <c r="Z27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="9" t="n"/>
-      <c r="AB27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="9" t="n"/>
-      <c r="AD27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="9" t="n"/>
-      <c r="AF27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="11" t="n">
+      <c r="P27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="10" t="n"/>
+      <c r="R27" s="11" t="n"/>
+      <c r="S27" s="10" t="n"/>
+      <c r="T27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="10" t="n"/>
+      <c r="V27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="10" t="n"/>
+      <c r="X27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="10" t="n"/>
+      <c r="Z27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="10" t="n"/>
+      <c r="AB27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="10" t="n"/>
+      <c r="AD27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="10" t="n"/>
+      <c r="AF27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="10" t="n"/>
+      <c r="AH27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="AH27" s="11" t="n">
+      <c r="AJ27" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>ADM-ACCESORIOS, PAQUETES Y PROGRAMAS</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="F28" s="14" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
         <is>
           <t>Compras de insumos, repuestos, etc</t>
         </is>
       </c>
-      <c r="H28" s="13" t="inlineStr">
+      <c r="J28" s="15" t="inlineStr">
         <is>
           <t>CRUZ TERMINIO, LUIS DANIEL</t>
         </is>
       </c>
-      <c r="I28" s="14" t="n">
+      <c r="K28" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="J28" s="15" t="n"/>
-      <c r="K28" s="14" t="n">
+      <c r="L28" s="17" t="n"/>
+      <c r="M28" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="L28" s="15" t="n">
+      <c r="N28" s="17" t="n">
         <v>787</v>
       </c>
-      <c r="M28" s="14" t="n">
+      <c r="O28" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="N28" s="15" t="n">
+      <c r="P28" s="17" t="n">
         <v>1215.56</v>
       </c>
-      <c r="O28" s="14" t="n">
+      <c r="Q28" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="P28" s="15" t="n">
+      <c r="R28" s="17" t="n">
         <v>887</v>
       </c>
-      <c r="Q28" s="14" t="n">
+      <c r="S28" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="R28" s="15" t="n">
+      <c r="T28" s="17" t="n">
         <v>718</v>
       </c>
-      <c r="S28" s="14" t="n">
+      <c r="U28" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="T28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" s="14" t="n">
+      <c r="V28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="V28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" s="14" t="n">
+      <c r="X28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="X28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="14" t="n">
+      <c r="Z28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="Z28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="14" t="n">
+      <c r="AB28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="AB28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="14" t="n">
+      <c r="AD28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="AD28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" s="14" t="n">
+      <c r="AF28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="AF28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" s="16" t="n">
+      <c r="AH28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="18" t="n">
         <v>6000</v>
       </c>
-      <c r="AH28" s="16" t="n">
+      <c r="AJ28" s="18" t="n">
         <v>3607.56</v>
       </c>
     </row>
@@ -3328,8 +3634,10 @@
           <t>ADM-ACCESORIOS, PAQUETES Y PROGRAMAS</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n">
-        <v>100</v>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
@@ -3341,7 +3649,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
@@ -3353,164 +3661,186 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
           <t>Kaspersky AISA</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>GRUPO OCTO S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="9" t="n"/>
-      <c r="L29" s="10" t="n"/>
-      <c r="M29" s="9" t="n"/>
-      <c r="N29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="9" t="n"/>
-      <c r="P29" s="10" t="n"/>
-      <c r="Q29" s="9" t="n"/>
-      <c r="R29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="9" t="n"/>
-      <c r="T29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="9" t="n"/>
-      <c r="V29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" s="9" t="n"/>
-      <c r="X29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="9" t="n"/>
-      <c r="Z29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="9" t="n"/>
-      <c r="AB29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="9" t="n">
+      <c r="K29" s="10" t="n"/>
+      <c r="L29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="10" t="n"/>
+      <c r="N29" s="11" t="n"/>
+      <c r="O29" s="10" t="n"/>
+      <c r="P29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="10" t="n"/>
+      <c r="R29" s="11" t="n"/>
+      <c r="S29" s="10" t="n"/>
+      <c r="T29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="10" t="n"/>
+      <c r="V29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="10" t="n"/>
+      <c r="X29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="10" t="n"/>
+      <c r="Z29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="10" t="n"/>
+      <c r="AB29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="10" t="n"/>
+      <c r="AD29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="10" t="n">
         <v>500</v>
       </c>
-      <c r="AD29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="9" t="n"/>
-      <c r="AF29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="11" t="n">
+      <c r="AF29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="10" t="n"/>
+      <c r="AH29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="12" t="n">
         <v>500</v>
       </c>
-      <c r="AH29" s="11" t="n">
+      <c r="AJ29" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>ADM-ACCESORIOS, PAQUETES Y PROGRAMAS</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>AISA Administración</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
+      <c r="F30" s="14" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
         <is>
           <t>Microsoft 365 IB</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr">
+      <c r="J30" s="15" t="inlineStr">
         <is>
           <t>DATA &amp; GRAPHICS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I30" s="14" t="n"/>
-      <c r="J30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="14" t="n"/>
-      <c r="L30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="14" t="n"/>
-      <c r="N30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="14" t="n"/>
-      <c r="P30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="14" t="n"/>
-      <c r="R30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="14" t="n"/>
-      <c r="T30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="14" t="n"/>
-      <c r="V30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" s="14" t="n"/>
-      <c r="X30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="14" t="n"/>
-      <c r="Z30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="14" t="n">
+      <c r="K30" s="16" t="n"/>
+      <c r="L30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="16" t="n"/>
+      <c r="N30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="16" t="n"/>
+      <c r="P30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="16" t="n"/>
+      <c r="R30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="16" t="n"/>
+      <c r="T30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="16" t="n"/>
+      <c r="V30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="16" t="n"/>
+      <c r="X30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="16" t="n"/>
+      <c r="Z30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="16" t="n"/>
+      <c r="AB30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="16" t="n">
         <v>1641.5</v>
       </c>
-      <c r="AB30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="14" t="n">
+      <c r="AD30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="16" t="n">
         <v>1641.5</v>
       </c>
-      <c r="AD30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" s="14" t="n">
+      <c r="AF30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="16" t="n">
         <v>1407</v>
       </c>
-      <c r="AF30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" s="16" t="n">
+      <c r="AH30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="18" t="n">
         <v>4690</v>
       </c>
-      <c r="AH30" s="16" t="n">
+      <c r="AJ30" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3520,8 +3850,10 @@
           <t>ADM-MANTENIMIENTO DE MOBILIARIO Y EQUIPO DE OFINA</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n">
-        <v>100</v>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
@@ -3533,7 +3865,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>Mantenimiento de mobiliario y equipo de ofina</t>
         </is>
@@ -3545,182 +3877,204 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
           <t>Mantenimiento informatico AISA</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>SERVICIOS TECNOLOGICOS E INFORMATICOS S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="9" t="n"/>
-      <c r="L31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="9" t="n">
+      <c r="K31" s="10" t="n"/>
+      <c r="L31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="10" t="n"/>
+      <c r="N31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="10" t="n">
         <v>640</v>
       </c>
-      <c r="N31" s="10" t="n"/>
-      <c r="O31" s="9" t="n"/>
-      <c r="P31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="9" t="n"/>
-      <c r="R31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="9" t="n">
+      <c r="P31" s="11" t="n"/>
+      <c r="Q31" s="10" t="n"/>
+      <c r="R31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="10" t="n"/>
+      <c r="T31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="10" t="n">
         <v>640</v>
       </c>
-      <c r="T31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="9" t="n"/>
-      <c r="V31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" s="9" t="n"/>
-      <c r="X31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="9" t="n">
+      <c r="V31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="10" t="n"/>
+      <c r="X31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="10" t="n"/>
+      <c r="Z31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="10" t="n">
         <v>640</v>
       </c>
-      <c r="Z31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="9" t="n"/>
-      <c r="AB31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="9" t="n"/>
-      <c r="AD31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" s="9" t="n">
+      <c r="AB31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="10" t="n"/>
+      <c r="AD31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="10" t="n"/>
+      <c r="AF31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="10" t="n">
         <v>640</v>
       </c>
-      <c r="AF31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" s="11" t="n">
+      <c r="AH31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="12" t="n">
         <v>2560</v>
       </c>
-      <c r="AH31" s="11" t="n">
+      <c r="AJ31" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>ADM-MANTENIMIENTO DE MOBILIARIO Y EQUIPO DE OFINA</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>AISA Administración</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>Mantenimiento de mobiliario y equipo de ofina</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F32" s="14" t="inlineStr">
         <is>
           <t>412010602</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr">
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
         <is>
           <t>Tecnico destacado KNK</t>
         </is>
       </c>
-      <c r="H32" s="13" t="inlineStr">
+      <c r="J32" s="15" t="inlineStr">
         <is>
           <t>KNK</t>
         </is>
       </c>
-      <c r="I32" s="14" t="n">
+      <c r="K32" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="J32" s="15" t="n"/>
-      <c r="K32" s="14" t="n">
+      <c r="L32" s="17" t="n"/>
+      <c r="M32" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="L32" s="15" t="n"/>
-      <c r="M32" s="14" t="n">
+      <c r="N32" s="17" t="n"/>
+      <c r="O32" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="N32" s="15" t="n"/>
-      <c r="O32" s="14" t="n">
+      <c r="P32" s="17" t="n"/>
+      <c r="Q32" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="P32" s="15" t="n"/>
-      <c r="Q32" s="14" t="n">
+      <c r="R32" s="17" t="n"/>
+      <c r="S32" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="R32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="14" t="n">
+      <c r="T32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="T32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="14" t="n">
+      <c r="V32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="V32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="14" t="n">
+      <c r="X32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="X32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="14" t="n">
+      <c r="Z32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="Z32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="14" t="n">
+      <c r="AB32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="AB32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="14" t="n">
+      <c r="AD32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="AD32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="14" t="n">
+      <c r="AF32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="AF32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" s="16" t="n">
+      <c r="AH32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="18" t="n">
         <v>1260</v>
       </c>
-      <c r="AH32" s="16" t="n">
+      <c r="AJ32" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3730,8 +4084,10 @@
           <t>ADM-MANTENIMIENTO DE MOBILIARIO Y EQUIPO DE OFINA</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n">
-        <v>100</v>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
@@ -3743,7 +4099,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>Mantenimiento de mobiliario y equipo de ofina</t>
         </is>
@@ -3755,204 +4111,226 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Desarrolladora</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
           <t>Casos de soporte en condominios</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>KNK</t>
         </is>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="K33" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="J33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="9" t="n">
+      <c r="L33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="L33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="9" t="n">
+      <c r="N33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="N33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="9" t="n">
+      <c r="P33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="P33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="9" t="n">
+      <c r="R33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="R33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="9" t="n">
+      <c r="T33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="T33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="9" t="n">
+      <c r="V33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="V33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="9" t="n">
+      <c r="X33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="X33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="9" t="n">
+      <c r="Z33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="Z33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="9" t="n">
+      <c r="AB33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="AB33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="9" t="n">
+      <c r="AD33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="AD33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" s="9" t="n">
+      <c r="AF33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="AF33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" s="11" t="n">
+      <c r="AH33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="12" t="n">
         <v>600</v>
       </c>
-      <c r="AH33" s="11" t="n">
+      <c r="AJ33" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>ADM-ACCESORIOS, PAQUETES Y PROGRAMAS</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n">
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>AISA Administración</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Accesorios, paquetes y programas</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>412010907</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>Compras de insumos, repuestos, etc</t>
+        </is>
+      </c>
+      <c r="J34" s="15" t="inlineStr">
+        <is>
+          <t>(-)</t>
+        </is>
+      </c>
+      <c r="K34" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>AISA Administración</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>Accesorios, paquetes y programas</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="inlineStr">
-        <is>
-          <t>412010907</t>
-        </is>
-      </c>
-      <c r="G34" s="13" t="inlineStr">
-        <is>
-          <t>Compras de insumos, repuestos, etc</t>
-        </is>
-      </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>(-)</t>
-        </is>
-      </c>
-      <c r="I34" s="14" t="n">
+      <c r="L34" s="17" t="n"/>
+      <c r="M34" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="J34" s="15" t="n"/>
-      <c r="K34" s="14" t="n">
+      <c r="N34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="L34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="14" t="n">
+      <c r="P34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="N34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="14" t="n">
+      <c r="R34" s="17" t="n"/>
+      <c r="S34" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="P34" s="15" t="n"/>
-      <c r="Q34" s="14" t="n">
+      <c r="T34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="R34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="14" t="n">
+      <c r="V34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="T34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="14" t="n">
+      <c r="X34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="V34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="14" t="n">
+      <c r="Z34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="X34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="14" t="n">
+      <c r="AB34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="Z34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="14" t="n">
+      <c r="AD34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="AB34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="14" t="n">
+      <c r="AF34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="AD34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="16" t="n">
+      <c r="AH34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="18" t="n">
         <v>1200</v>
       </c>
-      <c r="AH34" s="16" t="n">
+      <c r="AJ34" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3962,8 +4340,10 @@
           <t>ADM-ACCESORIOS, PAQUETES Y PROGRAMAS</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n">
-        <v>280</v>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
@@ -3975,7 +4355,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
@@ -3987,164 +4367,186 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
           <t>Pantallas interactivas (3) salas de reuniones</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>Por Cotizar</t>
         </is>
       </c>
-      <c r="I35" s="9" t="n">
+      <c r="K35" s="10" t="n">
         <v>4000</v>
       </c>
-      <c r="J35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="9" t="n"/>
-      <c r="L35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="9" t="n"/>
-      <c r="N35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="9" t="n"/>
-      <c r="P35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="9" t="n"/>
-      <c r="T35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="9" t="n"/>
-      <c r="V35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="9" t="n"/>
-      <c r="X35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="9" t="n"/>
-      <c r="Z35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="9" t="n"/>
-      <c r="AB35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="9" t="n"/>
-      <c r="AD35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="9" t="n"/>
-      <c r="AF35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="11" t="n">
+      <c r="L35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="10" t="n"/>
+      <c r="N35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="10" t="n"/>
+      <c r="P35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="10" t="n"/>
+      <c r="R35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="10" t="n"/>
+      <c r="T35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="10" t="n"/>
+      <c r="X35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="10" t="n"/>
+      <c r="Z35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="10" t="n"/>
+      <c r="AB35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="10" t="n"/>
+      <c r="AD35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="10" t="n"/>
+      <c r="AF35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="10" t="n"/>
+      <c r="AH35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="12" t="n">
         <v>4000</v>
       </c>
-      <c r="AH35" s="11" t="n">
+      <c r="AJ35" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>UDESA-SUSCRIPCIONES DE SOFTWARE</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>Suscripciones y publicaciones</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>412010905</t>
         </is>
       </c>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
         <is>
           <t>Policom Studio (2) Sala Panda y sala 2</t>
         </is>
       </c>
-      <c r="H36" s="13" t="inlineStr">
+      <c r="J36" s="15" t="inlineStr">
         <is>
           <t>Poly/HP</t>
         </is>
       </c>
-      <c r="I36" s="14" t="n">
+      <c r="K36" s="16" t="n">
         <v>1600</v>
       </c>
-      <c r="J36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="14" t="n"/>
-      <c r="L36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="14" t="n"/>
-      <c r="N36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="14" t="n"/>
-      <c r="P36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="14" t="n"/>
-      <c r="R36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="14" t="n"/>
-      <c r="T36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="14" t="n"/>
-      <c r="V36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" s="14" t="n"/>
-      <c r="X36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="14" t="n"/>
-      <c r="Z36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="14" t="n"/>
-      <c r="AB36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="14" t="n"/>
-      <c r="AD36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" s="14" t="n"/>
-      <c r="AF36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" s="16" t="n">
+      <c r="L36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="16" t="n"/>
+      <c r="N36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="16" t="n"/>
+      <c r="P36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="16" t="n"/>
+      <c r="R36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="16" t="n"/>
+      <c r="T36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="16" t="n"/>
+      <c r="V36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="16" t="n"/>
+      <c r="X36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="16" t="n"/>
+      <c r="Z36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="16" t="n"/>
+      <c r="AB36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="16" t="n"/>
+      <c r="AD36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="16" t="n"/>
+      <c r="AF36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="16" t="n"/>
+      <c r="AH36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="18" t="n">
         <v>1600</v>
       </c>
-      <c r="AH36" s="16" t="n">
+      <c r="AJ36" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4154,8 +4556,10 @@
           <t>UDESA-SUSCRIPCIONES DE SOFTWARE</t>
         </is>
       </c>
-      <c r="B37" s="8" t="n">
-        <v>280</v>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
@@ -4167,7 +4571,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>Suscripciones y publicaciones</t>
         </is>
@@ -4179,182 +4583,204 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
           <t>Almacenamiento extra Sharepoint (3000 GB)</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>DATA &amp; GRAPHICS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="9" t="n"/>
-      <c r="L37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="9" t="n"/>
-      <c r="N37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="9" t="n"/>
-      <c r="P37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="9" t="n"/>
-      <c r="R37" s="10" t="n">
+      <c r="K37" s="10" t="n"/>
+      <c r="L37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="10" t="n"/>
+      <c r="N37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="10" t="n"/>
+      <c r="P37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="10" t="n"/>
+      <c r="R37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="10" t="n"/>
+      <c r="T37" s="11" t="n">
         <v>490</v>
       </c>
-      <c r="S37" s="9" t="n"/>
-      <c r="T37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="9" t="n"/>
-      <c r="V37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="9" t="n"/>
-      <c r="X37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="9" t="n"/>
-      <c r="Z37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="9" t="n"/>
-      <c r="AB37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" s="9" t="n">
+      <c r="U37" s="10" t="n"/>
+      <c r="V37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="10" t="n"/>
+      <c r="X37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="10" t="n"/>
+      <c r="Z37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="10" t="n"/>
+      <c r="AB37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="10" t="n"/>
+      <c r="AD37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="10" t="n">
         <v>2600</v>
       </c>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="9" t="n">
+      <c r="AF37" s="11" t="n"/>
+      <c r="AG37" s="10" t="n">
         <v>2145</v>
       </c>
-      <c r="AF37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" s="11" t="n">
+      <c r="AH37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="12" t="n">
         <v>4745</v>
       </c>
-      <c r="AH37" s="11" t="n">
+      <c r="AJ37" s="12" t="n">
         <v>490</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>UDESA-SERVICIOS DE TECNOLOGÍA</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>Servicios Generales de Técnologia</t>
         </is>
       </c>
-      <c r="F38" s="13" t="inlineStr">
+      <c r="F38" s="14" t="inlineStr">
         <is>
           <t>412011220</t>
         </is>
       </c>
-      <c r="G38" s="13" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
         <is>
           <t>Zoom Hablemos</t>
         </is>
       </c>
-      <c r="H38" s="13" t="inlineStr">
+      <c r="J38" s="15" t="inlineStr">
         <is>
           <t>ZOOM VIDEO COMMUNICATIONS INC.</t>
         </is>
       </c>
-      <c r="I38" s="14" t="n">
+      <c r="K38" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="J38" s="15" t="n">
+      <c r="L38" s="17" t="n">
         <v>106.19</v>
       </c>
-      <c r="K38" s="14" t="n">
+      <c r="M38" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="L38" s="15" t="n">
+      <c r="N38" s="17" t="n">
         <v>106.2</v>
       </c>
-      <c r="M38" s="14" t="n">
+      <c r="O38" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="N38" s="15" t="n"/>
-      <c r="O38" s="14" t="n">
+      <c r="P38" s="17" t="n"/>
+      <c r="Q38" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="P38" s="15" t="n">
+      <c r="R38" s="17" t="n">
         <v>148.67</v>
       </c>
-      <c r="Q38" s="14" t="n">
+      <c r="S38" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="R38" s="15" t="n"/>
-      <c r="S38" s="14" t="n">
+      <c r="T38" s="17" t="n"/>
+      <c r="U38" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="T38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="14" t="n">
+      <c r="V38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="V38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" s="14" t="n">
+      <c r="X38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="X38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="14" t="n">
+      <c r="Z38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="Z38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="14" t="n">
+      <c r="AB38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AB38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="14" t="n">
+      <c r="AD38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AD38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="14" t="n">
+      <c r="AF38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AF38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" s="16" t="n">
+      <c r="AH38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="AH38" s="16" t="n">
+      <c r="AJ38" s="18" t="n">
         <v>361.0599999999999</v>
       </c>
     </row>
@@ -4364,8 +4790,10 @@
           <t>UDESA-SERVICIOS DE TECNOLOGÍA</t>
         </is>
       </c>
-      <c r="B39" s="8" t="n">
-        <v>280</v>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
@@ -4377,7 +4805,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>Servicios Generales de Técnologia</t>
         </is>
@@ -4389,180 +4817,202 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
           <t>Servicios de tecnologia (50% comparado a 2025)</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>JMTELCOM, JESUS MARTINEZ Y ASOCIADOS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I39" s="9" t="n">
+      <c r="K39" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="J39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="9" t="n">
+      <c r="L39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="L39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="9" t="n">
+      <c r="N39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="N39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="9" t="n">
+      <c r="P39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="P39" s="10" t="n"/>
-      <c r="Q39" s="9" t="n">
+      <c r="R39" s="11" t="n"/>
+      <c r="S39" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="R39" s="10" t="n">
+      <c r="T39" s="11" t="n">
         <v>349.28</v>
       </c>
-      <c r="S39" s="9" t="n">
+      <c r="U39" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="T39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" s="9" t="n">
+      <c r="V39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="V39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" s="9" t="n">
+      <c r="X39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="X39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="9" t="n">
+      <c r="Z39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="Z39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="9" t="n">
+      <c r="AB39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="AB39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="9" t="n">
+      <c r="AD39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="AD39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="9" t="n">
+      <c r="AF39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="AF39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" s="11" t="n">
+      <c r="AH39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="12" t="n">
         <v>4800</v>
       </c>
-      <c r="AH39" s="11" t="n">
+      <c r="AJ39" s="12" t="n">
         <v>349.28</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>UDESA-SERVICIOS DE TECNOLOGÍA</t>
         </is>
       </c>
-      <c r="B40" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>Servicios Generales de Técnologia</t>
         </is>
       </c>
-      <c r="F40" s="13" t="inlineStr">
+      <c r="F40" s="14" t="inlineStr">
         <is>
           <t>412011220</t>
         </is>
       </c>
-      <c r="G40" s="13" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
         <is>
           <t>Servicios de consumo de aws</t>
         </is>
       </c>
-      <c r="H40" s="13" t="inlineStr">
+      <c r="J40" s="15" t="inlineStr">
         <is>
           <t>Amazon Web Services</t>
         </is>
       </c>
-      <c r="I40" s="14" t="n"/>
-      <c r="J40" s="15" t="n"/>
-      <c r="K40" s="14" t="n"/>
-      <c r="L40" s="15" t="n">
+      <c r="K40" s="16" t="n"/>
+      <c r="L40" s="17" t="n"/>
+      <c r="M40" s="16" t="n"/>
+      <c r="N40" s="17" t="n">
         <v>769.92</v>
       </c>
-      <c r="M40" s="14" t="n"/>
-      <c r="N40" s="15" t="n">
+      <c r="O40" s="16" t="n"/>
+      <c r="P40" s="17" t="n">
         <v>343.79</v>
       </c>
-      <c r="O40" s="14" t="n"/>
-      <c r="P40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="14" t="n"/>
-      <c r="R40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="14" t="n"/>
-      <c r="T40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="14" t="n"/>
-      <c r="V40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" s="14" t="n"/>
-      <c r="X40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="14" t="n"/>
-      <c r="Z40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="14" t="n"/>
-      <c r="AB40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="14" t="n"/>
-      <c r="AD40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" s="14" t="n"/>
-      <c r="AF40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" s="16" t="n">
+      <c r="Q40" s="16" t="n"/>
+      <c r="R40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="16" t="n"/>
+      <c r="T40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="16" t="n"/>
+      <c r="V40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="16" t="n"/>
+      <c r="X40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="16" t="n"/>
+      <c r="Z40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="16" t="n"/>
+      <c r="AB40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="16" t="n"/>
+      <c r="AD40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="16" t="n"/>
+      <c r="AF40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="16" t="n"/>
+      <c r="AH40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="18" t="n">
         <v>1113.71</v>
       </c>
     </row>
@@ -4572,215 +5022,239 @@
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B41" s="8" t="n">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>Accesorios, paquetes y programas</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>412010907</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Licencias Modelo GPT (Empresa)</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>OpenAI, LLC</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="L41" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="M41" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="N41" s="11" t="n">
+        <v>180</v>
+      </c>
+      <c r="O41" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="P41" s="11" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q41" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="R41" s="11" t="n">
+        <v>175</v>
+      </c>
+      <c r="S41" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="T41" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>Tecnología</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>Accesorios, paquetes y programas</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>412010907</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>Licencias Modelo GPT (Empresa)</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>OpenAI, LLC</t>
-        </is>
-      </c>
-      <c r="I41" s="9" t="n">
+      <c r="U41" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="J41" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="K41" s="9" t="n">
+      <c r="V41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="L41" s="10" t="n">
-        <v>180</v>
-      </c>
-      <c r="M41" s="9" t="n">
+      <c r="X41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="N41" s="10" t="n">
-        <v>140</v>
-      </c>
-      <c r="O41" s="9" t="n">
+      <c r="Z41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="P41" s="10" t="n">
-        <v>175</v>
-      </c>
-      <c r="Q41" s="9" t="n">
+      <c r="AB41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="R41" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="S41" s="9" t="n">
+      <c r="AD41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="T41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" s="9" t="n">
+      <c r="AF41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="V41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="X41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="Z41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AD41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" s="11" t="n">
+      <c r="AH41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="12" t="n">
         <v>1440</v>
       </c>
-      <c r="AH41" s="11" t="n">
+      <c r="AJ41" s="12" t="n">
         <v>580</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B42" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <t>Tecnología</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F42" s="13" t="inlineStr">
+      <c r="F42" s="14" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G42" s="13" t="inlineStr">
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
         <is>
           <t>Licencia de team Heygen</t>
         </is>
       </c>
-      <c r="H42" s="13" t="inlineStr">
+      <c r="J42" s="15" t="inlineStr">
         <is>
           <t>HEYGEN TECHNOLOGY INC</t>
         </is>
       </c>
-      <c r="I42" s="14" t="n">
+      <c r="K42" s="16" t="n">
         <v>99</v>
       </c>
-      <c r="J42" s="15" t="n"/>
-      <c r="K42" s="14" t="n">
+      <c r="L42" s="17" t="n"/>
+      <c r="M42" s="16" t="n">
         <v>99</v>
       </c>
-      <c r="L42" s="15" t="n">
+      <c r="N42" s="17" t="n">
         <v>36.25</v>
       </c>
-      <c r="M42" s="14" t="n">
+      <c r="O42" s="16" t="n">
         <v>99</v>
       </c>
-      <c r="N42" s="15" t="n">
+      <c r="P42" s="17" t="n">
         <v>36.25</v>
       </c>
-      <c r="O42" s="14" t="n">
+      <c r="Q42" s="16" t="n">
         <v>99</v>
       </c>
-      <c r="P42" s="15" t="n"/>
-      <c r="Q42" s="14" t="n">
+      <c r="R42" s="17" t="n"/>
+      <c r="S42" s="16" t="n">
         <v>84</v>
       </c>
-      <c r="R42" s="15" t="n">
+      <c r="T42" s="17" t="n">
         <v>72.5</v>
       </c>
-      <c r="S42" s="14" t="n">
+      <c r="U42" s="16" t="n">
         <v>84</v>
       </c>
-      <c r="T42" s="15" t="n"/>
-      <c r="U42" s="14" t="n">
+      <c r="V42" s="17" t="n"/>
+      <c r="W42" s="16" t="n">
         <v>84</v>
       </c>
-      <c r="V42" s="15" t="n"/>
-      <c r="W42" s="14" t="n">
+      <c r="X42" s="17" t="n"/>
+      <c r="Y42" s="16" t="n">
         <v>84</v>
       </c>
-      <c r="X42" s="15" t="n"/>
-      <c r="Y42" s="14" t="n">
+      <c r="Z42" s="17" t="n"/>
+      <c r="AA42" s="16" t="n">
         <v>84</v>
       </c>
-      <c r="Z42" s="15" t="n"/>
-      <c r="AA42" s="14" t="n">
+      <c r="AB42" s="17" t="n"/>
+      <c r="AC42" s="16" t="n">
         <v>84</v>
       </c>
-      <c r="AB42" s="15" t="n"/>
-      <c r="AC42" s="14" t="n">
+      <c r="AD42" s="17" t="n"/>
+      <c r="AE42" s="16" t="n">
         <v>84</v>
       </c>
-      <c r="AD42" s="15" t="n"/>
-      <c r="AE42" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="15" t="n"/>
+      <c r="AF42" s="17" t="n"/>
       <c r="AG42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="17" t="n"/>
+      <c r="AI42" s="18" t="n">
         <v>984</v>
       </c>
-      <c r="AH42" s="16" t="n">
+      <c r="AJ42" s="18" t="n">
         <v>145</v>
       </c>
     </row>
@@ -4790,8 +5264,10 @@
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B43" s="8" t="n">
-        <v>25</v>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
@@ -4803,7 +5279,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
@@ -4815,160 +5291,182 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
           <t>Capacitación de IA Cursos</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>Udemy / Coursera</t>
         </is>
       </c>
-      <c r="I43" s="9" t="n">
+      <c r="K43" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="J43" s="10" t="n"/>
-      <c r="K43" s="9" t="n">
+      <c r="L43" s="11" t="n"/>
+      <c r="M43" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="L43" s="10" t="n"/>
-      <c r="M43" s="9" t="n">
+      <c r="N43" s="11" t="n"/>
+      <c r="O43" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="N43" s="10" t="n"/>
-      <c r="O43" s="9" t="n">
+      <c r="P43" s="11" t="n"/>
+      <c r="Q43" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="P43" s="10" t="n"/>
-      <c r="Q43" s="9" t="n">
+      <c r="R43" s="11" t="n"/>
+      <c r="S43" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="R43" s="10" t="n"/>
-      <c r="S43" s="9" t="n">
+      <c r="T43" s="11" t="n"/>
+      <c r="U43" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="T43" s="10" t="n"/>
-      <c r="U43" s="9" t="n">
+      <c r="V43" s="11" t="n"/>
+      <c r="W43" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="V43" s="10" t="n"/>
-      <c r="W43" s="9" t="n">
+      <c r="X43" s="11" t="n"/>
+      <c r="Y43" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="X43" s="10" t="n"/>
-      <c r="Y43" s="9" t="n">
+      <c r="Z43" s="11" t="n"/>
+      <c r="AA43" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="Z43" s="10" t="n"/>
-      <c r="AA43" s="9" t="n">
+      <c r="AB43" s="11" t="n"/>
+      <c r="AC43" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="AB43" s="10" t="n"/>
-      <c r="AC43" s="9" t="n">
+      <c r="AD43" s="11" t="n"/>
+      <c r="AE43" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="AD43" s="10" t="n"/>
-      <c r="AE43" s="9" t="n">
+      <c r="AF43" s="11" t="n"/>
+      <c r="AG43" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="AF43" s="10" t="n"/>
-      <c r="AG43" s="11" t="n">
+      <c r="AH43" s="11" t="n"/>
+      <c r="AI43" s="12" t="n">
         <v>600</v>
       </c>
-      <c r="AH43" s="11" t="n">
+      <c r="AJ43" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="C44" s="13" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>Tecnología</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F44" s="13" t="inlineStr">
+      <c r="F44" s="14" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G44" s="13" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
         <is>
           <t>Google AI Studio</t>
         </is>
       </c>
-      <c r="H44" s="13" t="inlineStr">
+      <c r="J44" s="15" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="I44" s="14" t="n">
+      <c r="K44" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="J44" s="15" t="n"/>
-      <c r="K44" s="14" t="n">
+      <c r="L44" s="17" t="n"/>
+      <c r="M44" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="L44" s="15" t="n"/>
-      <c r="M44" s="14" t="n">
+      <c r="N44" s="17" t="n"/>
+      <c r="O44" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="N44" s="15" t="n"/>
-      <c r="O44" s="14" t="n">
+      <c r="P44" s="17" t="n"/>
+      <c r="Q44" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="P44" s="15" t="n"/>
-      <c r="Q44" s="14" t="n">
+      <c r="R44" s="17" t="n"/>
+      <c r="S44" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="R44" s="15" t="n"/>
-      <c r="S44" s="14" t="n">
+      <c r="T44" s="17" t="n"/>
+      <c r="U44" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="T44" s="15" t="n"/>
-      <c r="U44" s="14" t="n">
+      <c r="V44" s="17" t="n"/>
+      <c r="W44" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="V44" s="15" t="n"/>
-      <c r="W44" s="14" t="n">
+      <c r="X44" s="17" t="n"/>
+      <c r="Y44" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="X44" s="15" t="n"/>
-      <c r="Y44" s="14" t="n">
+      <c r="Z44" s="17" t="n"/>
+      <c r="AA44" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="Z44" s="15" t="n"/>
-      <c r="AA44" s="14" t="n">
+      <c r="AB44" s="17" t="n"/>
+      <c r="AC44" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="AB44" s="15" t="n"/>
-      <c r="AC44" s="14" t="n">
+      <c r="AD44" s="17" t="n"/>
+      <c r="AE44" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="AD44" s="15" t="n"/>
-      <c r="AE44" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" s="15" t="n"/>
+      <c r="AF44" s="17" t="n"/>
       <c r="AG44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="17" t="n"/>
+      <c r="AI44" s="18" t="n">
         <v>220</v>
       </c>
-      <c r="AH44" s="16" t="n">
+      <c r="AJ44" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4978,8 +5476,10 @@
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B45" s="8" t="n">
-        <v>25</v>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
@@ -4991,7 +5491,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
@@ -5003,160 +5503,182 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
           <t>Capacitación de IA Cursos</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>Udemy / Coursera</t>
         </is>
       </c>
-      <c r="I45" s="9" t="n">
+      <c r="K45" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="J45" s="10" t="n"/>
-      <c r="K45" s="9" t="n">
+      <c r="L45" s="11" t="n"/>
+      <c r="M45" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="L45" s="10" t="n"/>
-      <c r="M45" s="9" t="n">
+      <c r="N45" s="11" t="n"/>
+      <c r="O45" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="N45" s="10" t="n"/>
-      <c r="O45" s="9" t="n">
+      <c r="P45" s="11" t="n"/>
+      <c r="Q45" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="P45" s="10" t="n"/>
-      <c r="Q45" s="9" t="n">
+      <c r="R45" s="11" t="n"/>
+      <c r="S45" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="R45" s="10" t="n"/>
-      <c r="S45" s="9" t="n">
+      <c r="T45" s="11" t="n"/>
+      <c r="U45" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="T45" s="10" t="n"/>
-      <c r="U45" s="9" t="n">
+      <c r="V45" s="11" t="n"/>
+      <c r="W45" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="V45" s="10" t="n"/>
-      <c r="W45" s="9" t="n">
+      <c r="X45" s="11" t="n"/>
+      <c r="Y45" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="X45" s="10" t="n"/>
-      <c r="Y45" s="9" t="n">
+      <c r="Z45" s="11" t="n"/>
+      <c r="AA45" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="Z45" s="10" t="n"/>
-      <c r="AA45" s="9" t="n">
+      <c r="AB45" s="11" t="n"/>
+      <c r="AC45" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="AB45" s="10" t="n"/>
-      <c r="AC45" s="9" t="n">
+      <c r="AD45" s="11" t="n"/>
+      <c r="AE45" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="AD45" s="10" t="n"/>
-      <c r="AE45" s="9" t="n">
+      <c r="AF45" s="11" t="n"/>
+      <c r="AG45" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="AF45" s="10" t="n"/>
-      <c r="AG45" s="11" t="n">
+      <c r="AH45" s="11" t="n"/>
+      <c r="AI45" s="12" t="n">
         <v>1500</v>
       </c>
-      <c r="AH45" s="11" t="n">
+      <c r="AJ45" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="A46" s="13" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B46" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="C46" s="13" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>Tecnología</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F46" s="13" t="inlineStr">
+      <c r="F46" s="14" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G46" s="13" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
         <is>
           <t>Licencias de Copilot personales</t>
         </is>
       </c>
-      <c r="H46" s="13" t="inlineStr">
+      <c r="J46" s="15" t="inlineStr">
         <is>
           <t>DATA &amp; GRAPHICS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I46" s="14" t="n">
+      <c r="K46" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="J46" s="15" t="n"/>
-      <c r="K46" s="14" t="n">
+      <c r="L46" s="17" t="n"/>
+      <c r="M46" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="L46" s="15" t="n"/>
-      <c r="M46" s="14" t="n">
+      <c r="N46" s="17" t="n"/>
+      <c r="O46" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="N46" s="15" t="n"/>
-      <c r="O46" s="14" t="n">
+      <c r="P46" s="17" t="n"/>
+      <c r="Q46" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="P46" s="15" t="n"/>
-      <c r="Q46" s="14" t="n">
+      <c r="R46" s="17" t="n"/>
+      <c r="S46" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="R46" s="15" t="n"/>
-      <c r="S46" s="14" t="n">
+      <c r="T46" s="17" t="n"/>
+      <c r="U46" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="T46" s="15" t="n"/>
-      <c r="U46" s="14" t="n">
+      <c r="V46" s="17" t="n"/>
+      <c r="W46" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="V46" s="15" t="n"/>
-      <c r="W46" s="14" t="n">
+      <c r="X46" s="17" t="n"/>
+      <c r="Y46" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="X46" s="15" t="n"/>
-      <c r="Y46" s="14" t="n">
+      <c r="Z46" s="17" t="n"/>
+      <c r="AA46" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="Z46" s="15" t="n"/>
-      <c r="AA46" s="14" t="n">
+      <c r="AB46" s="17" t="n"/>
+      <c r="AC46" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="AB46" s="15" t="n"/>
-      <c r="AC46" s="14" t="n">
+      <c r="AD46" s="17" t="n"/>
+      <c r="AE46" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="AD46" s="15" t="n"/>
-      <c r="AE46" s="14" t="n">
+      <c r="AF46" s="17" t="n"/>
+      <c r="AG46" s="16" t="n">
         <v>550</v>
       </c>
-      <c r="AF46" s="15" t="n"/>
-      <c r="AG46" s="16" t="n">
+      <c r="AH46" s="17" t="n"/>
+      <c r="AI46" s="18" t="n">
         <v>6600</v>
       </c>
-      <c r="AH46" s="16" t="n">
+      <c r="AJ46" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5166,8 +5688,10 @@
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B47" s="8" t="n">
-        <v>25</v>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
@@ -5179,7 +5703,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
@@ -5191,152 +5715,174 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
           <t>Licencia de Claude (anthropic)</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>ANTHROPIC, PBC</t>
         </is>
       </c>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="10" t="n"/>
-      <c r="K47" s="9" t="n"/>
-      <c r="L47" s="10" t="n"/>
-      <c r="M47" s="9" t="n"/>
-      <c r="N47" s="10" t="n"/>
-      <c r="O47" s="9" t="n"/>
-      <c r="P47" s="10" t="n"/>
-      <c r="Q47" s="9" t="n"/>
-      <c r="R47" s="10" t="n"/>
-      <c r="S47" s="9" t="n">
+      <c r="K47" s="10" t="n"/>
+      <c r="L47" s="11" t="n"/>
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="11" t="n"/>
+      <c r="O47" s="10" t="n"/>
+      <c r="P47" s="11" t="n"/>
+      <c r="Q47" s="10" t="n"/>
+      <c r="R47" s="11" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="11" t="n"/>
+      <c r="U47" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="T47" s="10" t="n">
+      <c r="V47" s="11" t="n">
         <v>125</v>
       </c>
-      <c r="U47" s="9" t="n">
+      <c r="W47" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="V47" s="10" t="n"/>
-      <c r="W47" s="9" t="n">
+      <c r="X47" s="11" t="n"/>
+      <c r="Y47" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="X47" s="10" t="n"/>
-      <c r="Y47" s="9" t="n">
+      <c r="Z47" s="11" t="n"/>
+      <c r="AA47" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="Z47" s="10" t="n"/>
-      <c r="AA47" s="9" t="n">
+      <c r="AB47" s="11" t="n"/>
+      <c r="AC47" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AB47" s="10" t="n"/>
-      <c r="AC47" s="9" t="n">
+      <c r="AD47" s="11" t="n"/>
+      <c r="AE47" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AD47" s="10" t="n"/>
-      <c r="AE47" s="9" t="n">
+      <c r="AF47" s="11" t="n"/>
+      <c r="AG47" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AF47" s="10" t="n"/>
-      <c r="AG47" s="11" t="n">
+      <c r="AH47" s="11" t="n"/>
+      <c r="AI47" s="12" t="n">
         <v>700</v>
       </c>
-      <c r="AH47" s="11" t="n">
+      <c r="AJ47" s="12" t="n">
         <v>125</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B48" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>Tecnología</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
+      <c r="F48" s="14" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G48" s="13" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
         <is>
           <t>Licencia Copilot Studio</t>
         </is>
       </c>
-      <c r="H48" s="13" t="inlineStr">
+      <c r="J48" s="15" t="inlineStr">
         <is>
           <t>DATA &amp; GRAPHICS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I48" s="14" t="n">
+      <c r="K48" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="J48" s="15" t="n"/>
-      <c r="K48" s="14" t="n">
+      <c r="L48" s="17" t="n"/>
+      <c r="M48" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="L48" s="15" t="n"/>
-      <c r="M48" s="14" t="n">
+      <c r="N48" s="17" t="n"/>
+      <c r="O48" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="N48" s="15" t="n"/>
-      <c r="O48" s="14" t="n">
+      <c r="P48" s="17" t="n"/>
+      <c r="Q48" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="P48" s="15" t="n"/>
-      <c r="Q48" s="14" t="n">
+      <c r="R48" s="17" t="n"/>
+      <c r="S48" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="R48" s="15" t="n"/>
-      <c r="S48" s="14" t="n">
+      <c r="T48" s="17" t="n"/>
+      <c r="U48" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="T48" s="15" t="n"/>
-      <c r="U48" s="14" t="n">
+      <c r="V48" s="17" t="n"/>
+      <c r="W48" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="V48" s="15" t="n"/>
-      <c r="W48" s="14" t="n">
+      <c r="X48" s="17" t="n"/>
+      <c r="Y48" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="X48" s="15" t="n"/>
-      <c r="Y48" s="14" t="n">
+      <c r="Z48" s="17" t="n"/>
+      <c r="AA48" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="Z48" s="15" t="n"/>
-      <c r="AA48" s="14" t="n">
+      <c r="AB48" s="17" t="n"/>
+      <c r="AC48" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="AB48" s="15" t="n"/>
-      <c r="AC48" s="14" t="n">
+      <c r="AD48" s="17" t="n"/>
+      <c r="AE48" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="AD48" s="15" t="n"/>
-      <c r="AE48" s="14" t="n">
+      <c r="AF48" s="17" t="n"/>
+      <c r="AG48" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="AF48" s="15" t="n"/>
-      <c r="AG48" s="16" t="n">
+      <c r="AH48" s="17" t="n"/>
+      <c r="AI48" s="18" t="n">
         <v>2400</v>
       </c>
-      <c r="AH48" s="16" t="n">
+      <c r="AJ48" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5346,8 +5892,10 @@
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B49" s="8" t="n">
-        <v>25</v>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
@@ -5359,7 +5907,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
@@ -5371,118 +5919,140 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
           <t>Likedin Learning</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>LINKEDIN IRELAND UNLIMITED COMPANY</t>
         </is>
       </c>
-      <c r="I49" s="9" t="n"/>
-      <c r="J49" s="10" t="n"/>
-      <c r="K49" s="9" t="n"/>
-      <c r="L49" s="10" t="n">
+      <c r="K49" s="10" t="n"/>
+      <c r="L49" s="11" t="n"/>
+      <c r="M49" s="10" t="n"/>
+      <c r="N49" s="11" t="n">
         <v>212.49</v>
       </c>
-      <c r="M49" s="9" t="n"/>
-      <c r="N49" s="10" t="n"/>
-      <c r="O49" s="9" t="n"/>
-      <c r="P49" s="10" t="n"/>
-      <c r="Q49" s="9" t="n"/>
-      <c r="R49" s="10" t="n"/>
-      <c r="S49" s="9" t="n"/>
-      <c r="T49" s="10" t="n"/>
-      <c r="U49" s="9" t="n"/>
-      <c r="V49" s="10" t="n"/>
-      <c r="W49" s="9" t="n"/>
-      <c r="X49" s="10" t="n"/>
-      <c r="Y49" s="9" t="n"/>
-      <c r="Z49" s="10" t="n"/>
-      <c r="AA49" s="9" t="n"/>
-      <c r="AB49" s="10" t="n"/>
-      <c r="AC49" s="9" t="n"/>
-      <c r="AD49" s="10" t="n"/>
-      <c r="AE49" s="9" t="n"/>
-      <c r="AF49" s="10" t="n"/>
-      <c r="AG49" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="11" t="n">
+      <c r="O49" s="10" t="n"/>
+      <c r="P49" s="11" t="n"/>
+      <c r="Q49" s="10" t="n"/>
+      <c r="R49" s="11" t="n"/>
+      <c r="S49" s="10" t="n"/>
+      <c r="T49" s="11" t="n"/>
+      <c r="U49" s="10" t="n"/>
+      <c r="V49" s="11" t="n"/>
+      <c r="W49" s="10" t="n"/>
+      <c r="X49" s="11" t="n"/>
+      <c r="Y49" s="10" t="n"/>
+      <c r="Z49" s="11" t="n"/>
+      <c r="AA49" s="10" t="n"/>
+      <c r="AB49" s="11" t="n"/>
+      <c r="AC49" s="10" t="n"/>
+      <c r="AD49" s="11" t="n"/>
+      <c r="AE49" s="10" t="n"/>
+      <c r="AF49" s="11" t="n"/>
+      <c r="AG49" s="10" t="n"/>
+      <c r="AH49" s="11" t="n"/>
+      <c r="AI49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="12" t="n">
         <v>212.49</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="A50" s="13" t="inlineStr">
         <is>
           <t>ADM-INTELIGENCIA ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B50" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>Tecnología</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
         <is>
           <t>Accesorios, paquetes y programas</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
+      <c r="F50" s="14" t="inlineStr">
         <is>
           <t>412010907</t>
         </is>
       </c>
-      <c r="G50" s="13" t="inlineStr">
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
         <is>
           <t>Power Automate licencia</t>
         </is>
       </c>
-      <c r="H50" s="13" t="inlineStr">
+      <c r="J50" s="15" t="inlineStr">
         <is>
           <t>DATA &amp; GRAPHICS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I50" s="14" t="n"/>
-      <c r="J50" s="15" t="n"/>
-      <c r="K50" s="14" t="n"/>
-      <c r="L50" s="15" t="n"/>
-      <c r="M50" s="14" t="n"/>
-      <c r="N50" s="15" t="n"/>
-      <c r="O50" s="14" t="n"/>
-      <c r="P50" s="15" t="n"/>
-      <c r="Q50" s="14" t="n"/>
-      <c r="R50" s="15" t="n">
+      <c r="K50" s="16" t="n"/>
+      <c r="L50" s="17" t="n"/>
+      <c r="M50" s="16" t="n"/>
+      <c r="N50" s="17" t="n"/>
+      <c r="O50" s="16" t="n"/>
+      <c r="P50" s="17" t="n"/>
+      <c r="Q50" s="16" t="n"/>
+      <c r="R50" s="17" t="n"/>
+      <c r="S50" s="16" t="n"/>
+      <c r="T50" s="17" t="n">
         <v>178.78</v>
       </c>
-      <c r="S50" s="14" t="n"/>
-      <c r="T50" s="15" t="n"/>
-      <c r="U50" s="14" t="n"/>
-      <c r="V50" s="15" t="n"/>
-      <c r="W50" s="14" t="n"/>
-      <c r="X50" s="15" t="n"/>
-      <c r="Y50" s="14" t="n"/>
-      <c r="Z50" s="15" t="n"/>
-      <c r="AA50" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" s="15" t="n"/>
-      <c r="AC50" s="14" t="n"/>
-      <c r="AD50" s="15" t="n"/>
-      <c r="AE50" s="14" t="n"/>
-      <c r="AF50" s="15" t="n"/>
-      <c r="AG50" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="16" t="n">
+      <c r="U50" s="16" t="n"/>
+      <c r="V50" s="17" t="n"/>
+      <c r="W50" s="16" t="n"/>
+      <c r="X50" s="17" t="n"/>
+      <c r="Y50" s="16" t="n"/>
+      <c r="Z50" s="17" t="n"/>
+      <c r="AA50" s="16" t="n"/>
+      <c r="AB50" s="17" t="n"/>
+      <c r="AC50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="17" t="n"/>
+      <c r="AE50" s="16" t="n"/>
+      <c r="AF50" s="17" t="n"/>
+      <c r="AG50" s="16" t="n"/>
+      <c r="AH50" s="17" t="n"/>
+      <c r="AI50" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="18" t="n">
         <v>178.78</v>
       </c>
     </row>
@@ -5492,8 +6062,10 @@
           <t>ADM-Licencias de programas</t>
         </is>
       </c>
-      <c r="B51" s="8" t="n">
-        <v>280</v>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
@@ -5505,205 +6077,203 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>INSTALACION DE EQUIPOS FORTINET EN LEASING</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>412010904</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr"/>
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr"/>
+      <c r="I51" s="9" t="inlineStr">
         <is>
           <t>LICENCIA ANUAL FIREWALL OF. CENTRALES /  DTE-1064</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
+      <c r="J51" s="9" t="inlineStr">
         <is>
           <t>JMTELCOM, JESUS MARTINEZ Y ASOCIADOS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I51" s="9" t="n"/>
-      <c r="J51" s="10" t="n"/>
-      <c r="K51" s="9" t="n"/>
-      <c r="L51" s="10" t="n"/>
-      <c r="M51" s="9" t="n"/>
-      <c r="N51" s="10" t="n"/>
-      <c r="O51" s="9" t="n"/>
-      <c r="P51" s="10" t="n">
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="11" t="n"/>
+      <c r="M51" s="10" t="n"/>
+      <c r="N51" s="11" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="11" t="n"/>
+      <c r="Q51" s="10" t="n"/>
+      <c r="R51" s="11" t="n">
         <v>5000</v>
       </c>
-      <c r="Q51" s="9" t="n"/>
-      <c r="R51" s="10" t="n"/>
-      <c r="S51" s="9" t="n"/>
-      <c r="T51" s="10" t="n"/>
-      <c r="U51" s="9" t="n"/>
-      <c r="V51" s="10" t="n"/>
-      <c r="W51" s="9" t="n"/>
-      <c r="X51" s="10" t="n"/>
-      <c r="Y51" s="9" t="n"/>
-      <c r="Z51" s="10" t="n"/>
-      <c r="AA51" s="9" t="n"/>
-      <c r="AB51" s="10" t="n"/>
-      <c r="AC51" s="9" t="n"/>
-      <c r="AD51" s="10" t="n"/>
-      <c r="AE51" s="9" t="n"/>
-      <c r="AF51" s="10" t="n"/>
-      <c r="AG51" s="11" t="n"/>
-      <c r="AH51" s="11" t="n">
+      <c r="S51" s="10" t="n"/>
+      <c r="T51" s="11" t="n"/>
+      <c r="U51" s="10" t="n"/>
+      <c r="V51" s="11" t="n"/>
+      <c r="W51" s="10" t="n"/>
+      <c r="X51" s="11" t="n"/>
+      <c r="Y51" s="10" t="n"/>
+      <c r="Z51" s="11" t="n"/>
+      <c r="AA51" s="10" t="n"/>
+      <c r="AB51" s="11" t="n"/>
+      <c r="AC51" s="10" t="n"/>
+      <c r="AD51" s="11" t="n"/>
+      <c r="AE51" s="10" t="n"/>
+      <c r="AF51" s="11" t="n"/>
+      <c r="AG51" s="10" t="n"/>
+      <c r="AH51" s="11" t="n"/>
+      <c r="AI51" s="12" t="n"/>
+      <c r="AJ51" s="12" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>UDESA-Servicios de Tecnología</t>
         </is>
       </c>
-      <c r="B52" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="C52" s="13" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
         <is>
           <t>Unidad Desarrolladora</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
         <is>
           <t>INSTALACION DE EQUIPOS FORTINET EN LEASING</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
-        <is>
-          <t>412011220</t>
-        </is>
-      </c>
-      <c r="G52" s="13" t="inlineStr">
+      <c r="F52" s="14" t="inlineStr"/>
+      <c r="G52" s="14" t="inlineStr"/>
+      <c r="H52" s="14" t="inlineStr"/>
+      <c r="I52" s="15" t="inlineStr">
         <is>
           <t>INTALACION DE EQUOPOS /  DTE-0900</t>
         </is>
       </c>
-      <c r="H52" s="13" t="inlineStr">
+      <c r="J52" s="15" t="inlineStr">
         <is>
           <t>JMTELCOM, JESUS MARTINEZ Y ASOCIADOS, S.A. DE C. V.</t>
         </is>
       </c>
-      <c r="I52" s="14" t="n"/>
-      <c r="J52" s="15" t="n"/>
-      <c r="K52" s="14" t="n"/>
-      <c r="L52" s="15" t="n"/>
-      <c r="M52" s="14" t="n"/>
-      <c r="N52" s="15" t="n"/>
-      <c r="O52" s="14" t="n"/>
-      <c r="P52" s="15" t="n">
+      <c r="K52" s="16" t="n"/>
+      <c r="L52" s="17" t="n"/>
+      <c r="M52" s="16" t="n"/>
+      <c r="N52" s="17" t="n"/>
+      <c r="O52" s="16" t="n"/>
+      <c r="P52" s="17" t="n"/>
+      <c r="Q52" s="16" t="n"/>
+      <c r="R52" s="17" t="n">
         <v>1895</v>
       </c>
-      <c r="Q52" s="14" t="n"/>
-      <c r="R52" s="15" t="n"/>
-      <c r="S52" s="14" t="n"/>
-      <c r="T52" s="15" t="n"/>
-      <c r="U52" s="14" t="n"/>
-      <c r="V52" s="15" t="n"/>
-      <c r="W52" s="14" t="n"/>
-      <c r="X52" s="15" t="n"/>
-      <c r="Y52" s="14" t="n"/>
-      <c r="Z52" s="15" t="n"/>
-      <c r="AA52" s="14" t="n"/>
-      <c r="AB52" s="15" t="n"/>
-      <c r="AC52" s="14" t="n"/>
-      <c r="AD52" s="15" t="n"/>
-      <c r="AE52" s="14" t="n"/>
-      <c r="AF52" s="15" t="n"/>
+      <c r="S52" s="16" t="n"/>
+      <c r="T52" s="17" t="n"/>
+      <c r="U52" s="16" t="n"/>
+      <c r="V52" s="17" t="n"/>
+      <c r="W52" s="16" t="n"/>
+      <c r="X52" s="17" t="n"/>
+      <c r="Y52" s="16" t="n"/>
+      <c r="Z52" s="17" t="n"/>
+      <c r="AA52" s="16" t="n"/>
+      <c r="AB52" s="17" t="n"/>
+      <c r="AC52" s="16" t="n"/>
+      <c r="AD52" s="17" t="n"/>
+      <c r="AE52" s="16" t="n"/>
+      <c r="AF52" s="17" t="n"/>
       <c r="AG52" s="16" t="n"/>
-      <c r="AH52" s="16" t="n">
+      <c r="AH52" s="17" t="n"/>
+      <c r="AI52" s="18" t="n"/>
+      <c r="AJ52" s="18" t="n">
         <v>1895</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>TOTAL GENERAL</t>
         </is>
       </c>
-      <c r="I53" s="18" t="n">
+      <c r="K53" s="20" t="n">
         <v>20527.1</v>
       </c>
-      <c r="J53" s="18" t="n">
+      <c r="L53" s="20" t="n">
         <v>22376.19</v>
       </c>
-      <c r="K53" s="18" t="n">
+      <c r="M53" s="20" t="n">
         <v>13247.1</v>
       </c>
-      <c r="L53" s="18" t="n">
+      <c r="N53" s="20" t="n">
         <v>10585.29</v>
       </c>
-      <c r="M53" s="18" t="n">
+      <c r="O53" s="20" t="n">
         <v>17047.1</v>
       </c>
-      <c r="N53" s="18" t="n">
+      <c r="P53" s="20" t="n">
         <v>10541.76</v>
       </c>
-      <c r="O53" s="18" t="n">
+      <c r="Q53" s="20" t="n">
         <v>14027.1</v>
       </c>
-      <c r="P53" s="18" t="n">
+      <c r="R53" s="20" t="n">
         <v>12640.61</v>
       </c>
-      <c r="Q53" s="18" t="n">
+      <c r="S53" s="20" t="n">
         <v>13782.1</v>
       </c>
-      <c r="R53" s="18" t="n">
+      <c r="T53" s="20" t="n">
         <v>13928.05</v>
       </c>
-      <c r="S53" s="18" t="n">
+      <c r="U53" s="20" t="n">
         <v>16112.1</v>
       </c>
-      <c r="T53" s="18" t="n">
+      <c r="V53" s="20" t="n">
         <v>3625</v>
       </c>
-      <c r="U53" s="18" t="n">
+      <c r="W53" s="20" t="n">
         <v>14962.1</v>
       </c>
-      <c r="V53" s="18" t="n"/>
-      <c r="W53" s="18" t="n">
+      <c r="X53" s="20" t="n"/>
+      <c r="Y53" s="20" t="n">
         <v>13332.1</v>
       </c>
-      <c r="X53" s="18" t="n"/>
-      <c r="Y53" s="18" t="n">
+      <c r="Z53" s="20" t="n"/>
+      <c r="AA53" s="20" t="n">
         <v>16662.1</v>
       </c>
-      <c r="Z53" s="18" t="n"/>
-      <c r="AA53" s="18" t="n">
+      <c r="AB53" s="20" t="n"/>
+      <c r="AC53" s="20" t="n">
         <v>41353.6</v>
       </c>
-      <c r="AB53" s="18" t="n"/>
-      <c r="AC53" s="18" t="n">
+      <c r="AD53" s="20" t="n"/>
+      <c r="AE53" s="20" t="n">
         <v>19123.6</v>
       </c>
-      <c r="AD53" s="18" t="n"/>
-      <c r="AE53" s="18" t="n">
+      <c r="AF53" s="20" t="n"/>
+      <c r="AG53" s="20" t="n">
         <v>20410.1</v>
       </c>
-      <c r="AF53" s="18" t="n"/>
-      <c r="AG53" s="18" t="n">
+      <c r="AH53" s="20" t="n"/>
+      <c r="AI53" s="20" t="n">
         <v>220586.2</v>
       </c>
-      <c r="AH53" s="18" t="n">
+      <c r="AJ53" s="20" t="n">
         <v>80983.17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A53:J53"/>
     <mergeCell ref="A2:AH2"/>
     <mergeCell ref="A1:AH1"/>
-    <mergeCell ref="A53:H53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
